--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source and Method'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.62549090385437</v>
+        <v>2.622556209564209</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68250560760498</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285938558352174</v>
+        <v>0.0228591470497912</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285938558352174</v>
+        <v>2.28591470497912</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68250560760498</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499260425567627</v>
+        <v>2.496466398239136</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935283243179036</v>
+        <v>-0.06935277556863939</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935283243179036</v>
+        <v>-6.935277556863939</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499260425567627</v>
+        <v>2.496466398239136</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739734649658</v>
+        <v>2.67974066734314</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0734134415145471</v>
+        <v>0.07341347323291636</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.34134415145471</v>
+        <v>7.341347323291636</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739734649658</v>
+        <v>2.67974066734314</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.565841436386108</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250421205546351</v>
+        <v>-0.04250382596535285</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250421205546351</v>
+        <v>-4.250382596535285</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.565841436386108</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558812379837036</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854462412563477</v>
+        <v>0.3854459413790421</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54462412563478</v>
+        <v>38.54459413790421</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558812379837036</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.56398868560791</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454503699099385</v>
+        <v>0.001454655740082078</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1454503699099385</v>
+        <v>0.1454655740082078</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.56398868560791</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006528854370117</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699140486252</v>
+        <v>0.1241696717852019</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41699140486252</v>
+        <v>12.41696717852019</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006528854370117</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356164383561634</v>
+        <v>0.04356189773556429</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356164383561634</v>
+        <v>4.356189773556429</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411285400390625</v>
+        <v>4.40635347366333</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506392446076891</v>
+        <v>0.05506341882685883</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506392446076891</v>
+        <v>5.506341882685883</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411285400390625</v>
+        <v>4.40635347366333</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.097486972808838</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568497101328961</v>
+        <v>0.1568493093612204</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.6849710132896</v>
+        <v>15.68493093612204</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.097486972808838</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956111431121826</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882171416760748</v>
+        <v>-0.02882105628470177</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882171416760748</v>
+        <v>-2.882105628470177</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956111431121826</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.772735595703125</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592256053872533</v>
+        <v>-0.03592239798838426</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592256053872533</v>
+        <v>-3.592239798838426</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.772735595703125</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.062729358673096</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702841717105691</v>
+        <v>0.2702839361416431</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02841717105691</v>
+        <v>27.02839361416432</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.062729358673096</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979395866394043</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484755857082565</v>
+        <v>-0.01484773445048615</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484755857082565</v>
+        <v>-1.484773445048615</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979395866394043</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722181797027588</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.0430167319765653</v>
+        <v>-0.04301657298715189</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.30167319765653</v>
+        <v>-4.301657298715189</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722181797027588</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556883811950684</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888723059494003</v>
+        <v>-0.02888710249012416</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888723059494003</v>
+        <v>-2.888710249012416</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556883811950684</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.228055953979492</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363097163717</v>
+        <v>0.1220360864374244</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20363097163717</v>
+        <v>12.20360864374244</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.228055953979492</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857003688812256</v>
+        <v>5.850456237792969</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062873724857742</v>
+        <v>-0.06062882526693603</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062873724857742</v>
+        <v>-6.062882526693603</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857003688812256</v>
+        <v>5.850456237792969</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.047036647796631</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360051231671157</v>
+        <v>0.03360086837908227</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360051231671157</v>
+        <v>3.360086837908227</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.047036647796631</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.94319486618042</v>
+        <v>6.935433864593506</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.146914757174905</v>
+        <v>0.1469144753935934</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.6914757174905</v>
+        <v>14.69144753935934</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.94319486618042</v>
+        <v>6.935433864593506</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211391988220623</v>
+        <v>0.001211166243223705</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211391988220623</v>
+        <v>0.1211166243223705</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215311527252197</v>
+        <v>5.209483623504639</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497688045483735</v>
+        <v>-0.2497683912712815</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97688045483735</v>
+        <v>-24.97683912712815</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215311527252197</v>
+        <v>5.209483623504639</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.046820640563965</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240500650023255</v>
+        <v>-0.2240500045812026</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40500650023255</v>
+        <v>-22.40500045812026</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.046820640563965</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831363842994731</v>
+        <v>-0.183136818674309</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31363842994731</v>
+        <v>-18.3136818674309</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677881889603055</v>
+        <v>0.07677904068510788</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677881889603055</v>
+        <v>7.677904068510788</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.819417715072632</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421897082719897</v>
+        <v>0.07421900381634172</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421897082719897</v>
+        <v>7.421900381634172</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.819417715072632</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640088082323901</v>
+        <v>0.1640089866296075</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40088082323901</v>
+        <v>16.40089866296075</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486505031585693</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019797673586959</v>
+        <v>0.008019546108555708</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019797673586959</v>
+        <v>0.8019546108555708</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486505031585693</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.357765674591064</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507481493818129</v>
+        <v>-0.2507479491647804</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07481493818129</v>
+        <v>-25.07479491647804</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.357765674591064</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.070911407470703</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123879532281372</v>
+        <v>0.2123869864642927</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23879532281372</v>
+        <v>21.23869864642927</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.070911407470703</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186889171600342</v>
+        <v>4.182209491729736</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733922257928567</v>
+        <v>0.02733984435396586</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733922257928567</v>
+        <v>2.733984435396586</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186889171600342</v>
+        <v>4.182209491729736</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160976886749268</v>
+        <v>4.156326770782471</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188911095817207</v>
+        <v>-0.006188767205097756</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188911095817207</v>
+        <v>-0.6188767205097756</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160976886749268</v>
+        <v>4.156326770782471</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.319096088409424</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.0391620591824553</v>
+        <v>0.03916181922248385</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.91620591824553</v>
+        <v>3.916181922248385</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.319096088409424</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.987789630889893</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548229768248279</v>
+        <v>0.154822566757649</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48229768248279</v>
+        <v>15.4822566757649</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.987789630889893</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899645736355199</v>
+        <v>0.07899683685315129</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899645736355199</v>
+        <v>7.899683685315129</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563282285618801</v>
+        <v>0.08563278232560179</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563282285618801</v>
+        <v>8.56327823256018</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877295970916748</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802197433110722</v>
+        <v>0.004802348231823794</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4802197433110722</v>
+        <v>0.4802348231823794</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877295970916748</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.710042476654053</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429664625194604</v>
+        <v>0.1429661787258361</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29664625194604</v>
+        <v>14.29661787258361</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.710042476654053</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395680836540848</v>
+        <v>-0.02395654513128542</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395680836540848</v>
+        <v>-2.395654513128542</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.26999044418335</v>
+        <v>7.261864185333252</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088013721369481</v>
+        <v>0.1088012308531945</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88013721369481</v>
+        <v>10.88012308531945</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.26999044418335</v>
+        <v>7.261864185333252</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830543518066406</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146568260115995</v>
+        <v>0.214656969264309</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46568260115995</v>
+        <v>21.4656969264309</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830543518066406</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.453957557678223</v>
+        <v>9.443387031555176</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059747096386237</v>
+        <v>0.07059699667439601</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059747096386237</v>
+        <v>7.059699667439601</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.453957557678223</v>
+        <v>9.443387031555176</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176066076792814</v>
+        <v>0.1176071683315141</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76066076792814</v>
+        <v>11.76071683315141</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282806396484</v>
+        <v>13.29794979095459</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599917862993668</v>
+        <v>0.2599918060250836</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99917862993668</v>
+        <v>25.99918060250836</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282806396484</v>
+        <v>13.29794979095459</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47214031219482</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196682233590973</v>
+        <v>0.01196672870330273</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196682233590973</v>
+        <v>1.196672870330273</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47214031219482</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47994041442871</v>
+        <v>12.465989112854</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364827523864081</v>
+        <v>-0.07364847598012692</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364827523864081</v>
+        <v>-7.364847598012691</v>
       </c>
     </row>
     <row r="48">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47994041442871</v>
+        <v>12.465989112854</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.3436975479126</v>
+        <v>13.32878017425537</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921163922267226</v>
+        <v>0.06921160074748678</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921163922267226</v>
+        <v>6.921160074748678</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.3436975479126</v>
+        <v>13.32878017425537</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253009796143</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556768457364667</v>
+        <v>-0.02556732179522692</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.556768457364667</v>
+        <v>-2.556732179522692</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253009796143</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998041314080548</v>
+        <v>-0.004998199561433103</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998041314080548</v>
+        <v>-0.4998199561433103</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65938091278076</v>
+        <v>13.64411449432373</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579405627172118</v>
+        <v>0.05579413045721027</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579405627172118</v>
+        <v>5.579413045721027</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65938091278076</v>
+        <v>13.64411449432373</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.0263693823436163</v>
+        <v>-0.02636960049531378</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.63693823436163</v>
+        <v>-2.636960049531378</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.93761920928955</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544633344791</v>
+        <v>0.1244545437838092</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44544633344791</v>
+        <v>12.44545437838092</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.93761920928955</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479347229004</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.0822810403859966</v>
+        <v>0.08228130993934912</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.22810403859966</v>
+        <v>8.228130993934911</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479347229004</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355560302734</v>
+        <v>19.91127014160156</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316224879332291</v>
+        <v>0.2316219541977889</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16224879332292</v>
+        <v>23.16219541977889</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355560302734</v>
+        <v>19.91127014160156</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517193695026387</v>
+        <v>-0.02517175579831477</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517193695026387</v>
+        <v>-2.517175579831477</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31177139282227</v>
+        <v>22.28683471679688</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482098192612498</v>
+        <v>0.1482099974588429</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82098192612498</v>
+        <v>14.82099974588429</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31177139282227</v>
+        <v>22.28683471679688</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.62515830993652</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455892965801925</v>
+        <v>-0.07455865437939457</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455892965801924</v>
+        <v>-7.455865437939457</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.62515830993652</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341668407136812</v>
+        <v>0.2341664229132356</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41668407136812</v>
+        <v>23.41664229132356</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.53269577026367</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537130761895</v>
+        <v>0.2780535014795418</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80537130761896</v>
+        <v>27.80535014795418</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.53269577026367</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.0998100797688396</v>
+        <v>-0.09980991413127971</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.98100797688396</v>
+        <v>-9.98099141312797</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40888595581055</v>
+        <v>24.3816089630127</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.167454434811324</v>
+        <v>-0.1674542959030992</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.7454434811324</v>
+        <v>-16.74542959030993</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40888595581055</v>
+        <v>24.3816089630127</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820846557617</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124624549298961</v>
+        <v>-0.004124858161063338</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124624549298961</v>
+        <v>-0.4124858161063338</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820846557617</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571079042555</v>
+        <v>0.1191571387757528</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91571079042555</v>
+        <v>11.91571387757529</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.47107696533203</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741339540492</v>
+        <v>-0.3202739802562728</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02741339540493</v>
+        <v>-32.02739802562728</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.47107696533203</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61636924743652</v>
+        <v>18.59556198120117</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739661008697384</v>
+        <v>0.006739456291735557</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739661008697384</v>
+        <v>0.6739456291735557</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61636924743652</v>
+        <v>18.59556198120117</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.10013675689697</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709813357917</v>
+        <v>-0.1879709377881579</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79709813357917</v>
+        <v>-18.79709377881579</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.10013675689697</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.19816581003128</v>
+        <v>0.1981658545877099</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.816581003128</v>
+        <v>19.81658545877099</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.03538513183594</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689697973216241</v>
+        <v>-0.1689699318887956</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89697973216241</v>
+        <v>-16.89699318887956</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.03538513183594</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.09545421600342</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955340888197248</v>
+        <v>-0.1955341276631157</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55340888197248</v>
+        <v>-19.55341276631157</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.09545421600342</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363258361816</v>
+        <v>13.44858360290527</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708414046692</v>
+        <v>0.1118709031291722</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18708414046692</v>
+        <v>11.18709031291722</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363258361816</v>
+        <v>13.44858360290527</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.88548278808594</v>
+        <v>16.86660766601562</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541550494055593</v>
+        <v>0.254154947765054</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41550494055593</v>
+        <v>25.4154947765054</v>
       </c>
     </row>
     <row r="73">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.88548278808594</v>
+        <v>16.86660766601562</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5653018951416</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415619095126</v>
+        <v>-0.1364415308901092</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64415619095126</v>
+        <v>-13.64415308901092</v>
       </c>
     </row>
     <row r="74">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.5653018951416</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.47190284729004</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368687351278623</v>
+        <v>0.3368691557148624</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68687351278623</v>
+        <v>33.68691557148624</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.47190284729004</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16453170776367</v>
+        <v>23.13863563537598</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883094302655908</v>
+        <v>0.1883089093471031</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83094302655908</v>
+        <v>18.83089093471031</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16453170776367</v>
+        <v>23.13863563537598</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012138366699</v>
+        <v>27.68914222717285</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966622823795958</v>
+        <v>0.1966627014446669</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66622823795958</v>
+        <v>19.66627014446669</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012138366699</v>
+        <v>27.68914222717285</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.00100795915484464</v>
+        <v>-0.001008053614069193</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.100795915484464</v>
+        <v>-0.1008053614069193</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.75653076171875</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365332711422</v>
+        <v>0.363436428780211</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34365332711423</v>
+        <v>36.3436428780211</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.75653076171875</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105081934617</v>
+        <v>0.1182106865009505</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82105081934617</v>
+        <v>11.82106865009505</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.58600997924805</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046523499921483</v>
+        <v>0.1046520284189869</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46523499921483</v>
+        <v>10.46520284189869</v>
       </c>
     </row>
     <row r="81">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.58600997924805</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619638947121319</v>
+        <v>0.05619655619364927</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619638947121319</v>
+        <v>5.619655619364927</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185780952231065</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85780613309324</v>
+        <v>-11.85780952231065</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.70406341552734</v>
+        <v>40.65856170654297</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250716057470163</v>
+        <v>-0.062507267540302</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250716057470163</v>
+        <v>-6.2507267540302</v>
       </c>
     </row>
     <row r="84">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.70406341552734</v>
+        <v>40.65856170654297</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.63073348999023</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468858589700071</v>
+        <v>0.1468859579084962</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68858589700071</v>
+        <v>14.68859579084962</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.63073348999023</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43413162231445</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893412834461786</v>
+        <v>0.05893414142888309</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893412834461786</v>
+        <v>5.893414142888309</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43413162231445</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175241944488</v>
+        <v>0.2424175564739466</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24175241944489</v>
+        <v>24.24175564739466</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97162628173828</v>
+        <v>78.88337707519531</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858094213803009</v>
+        <v>0.2858097587910202</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58094213803009</v>
+        <v>28.58097587910202</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97162628173828</v>
+        <v>78.88337707519531</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421812779074114</v>
+        <v>0.1421810468342366</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21812779074114</v>
+        <v>14.21810468342366</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.25273895263672</v>
+        <v>86.15634155273438</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.0437602868993443</v>
+        <v>-0.04376022325813289</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.37602868993443</v>
+        <v>-4.376022325813289</v>
       </c>
     </row>
     <row r="90">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.25273895263672</v>
+        <v>86.15634155273438</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4435958862305</v>
+        <v>109.3212738037109</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688709624204324</v>
+        <v>0.2688708902152934</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88709624204324</v>
+        <v>26.88708902152934</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4435958862305</v>
+        <v>109.3212738037109</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367309570312</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269433351334972</v>
+        <v>0.1269432152707823</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69433351334972</v>
+        <v>12.69432152707823</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367309570312</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.8274383544922</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277659422323111</v>
+        <v>-0.05277657397651536</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277659422323111</v>
+        <v>-5.277657397651536</v>
       </c>
     </row>
     <row r="93">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.8274383544922</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008212771048568</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008208031891745</v>
+        <v>2.008212771048568</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.1150207519531</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742813318985359</v>
+        <v>0.01742808690201669</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.742813318985359</v>
+        <v>1.742808690201669</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.1150207519531</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.4047546386719</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321460769799583</v>
+        <v>0.09321497710709581</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321460769799582</v>
+        <v>9.321497710709581</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.4047546386719</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135301258146518</v>
+        <v>0.04135259928286272</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135301258146518</v>
+        <v>4.135259928286272</v>
       </c>
     </row>
     <row r="97">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691468412549</v>
+        <v>-0.02857691133769347</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857691468412549</v>
+        <v>-2.857691133769347</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902751059577</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58902751059577</v>
+        <v>-10.58901794305278</v>
       </c>
     </row>
     <row r="99">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039318634820721</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039309306242167</v>
+        <v>4.039318634820721</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.2283248901367</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323250437332495</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249309931265</v>
+        <v>-13.23250437332495</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.2283248901367</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -3883,13 +3883,13 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982410811787075</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.4982410811787075</v>
+        <v>0.4982481462220356</v>
       </c>
     </row>
     <row r="102">
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.64599609375</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.2406354069759602</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.06355273027898</v>
+        <v>24.06354069759602</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.603515625</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516823827925</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92515633256428</v>
+        <v>16.92516823827926</v>
       </c>
     </row>
     <row r="104">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.603515625</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258305979143173</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58306729394936</v>
+        <v>12.58305979143173</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074555918313137</v>
+        <v>-2.07454681313487</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125121360969189</v>
+        <v>7.125119707459349</v>
       </c>
     </row>
     <row r="107">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.0852717678839181</v>
+        <v>0.08527167560685012</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>8.527176788391809</v>
+        <v>8.527167560685012</v>
       </c>
     </row>
     <row r="108">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4121,13 +4121,13 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.125882777513319</v>
+        <v>-0.1258827644807442</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.5882777513319</v>
+        <v>-12.58827644807442</v>
       </c>
     </row>
     <row r="109">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.05373099736807707</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>5.373101785259271</v>
+        <v>5.373099736807707</v>
       </c>
     </row>
     <row r="110">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -4189,13 +4189,13 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482579447315181</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>2.482573320254033</v>
+        <v>2.482579447315181</v>
       </c>
     </row>
     <row r="111">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293465552553402</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>-7.293465552553402</v>
+        <v>-7.293472316669725</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925510196515</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-1.56925510196515</v>
+        <v>-1.56925888464382</v>
       </c>
     </row>
     <row r="113">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234085538123</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>14.43234085538123</v>
+        <v>14.43234709050238</v>
       </c>
     </row>
     <row r="114">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>210.8942108154297</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797465881657349</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.797465881657349</v>
+        <v>5.797470065579535</v>
       </c>
     </row>
     <row r="115">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>210.8942108154297</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="F115" s="3" t="n">
-        <v>200.0899963378906</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>-0.05123049341072095</v>
+        <v>-0.05123052301166586</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>-5.123049341072095</v>
+        <v>-5.123052301166586</v>
       </c>
     </row>
     <row r="116">
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>200.0899963378906</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -4393,17 +4393,51 @@
         </is>
       </c>
       <c r="F116" s="3" t="n">
-        <v>200.75</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0.003298534030631073</v>
+        <v>0.003298560492809743</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0.3298534030631073</v>
+        <v>0.3298560492809743</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>200.5256195068359</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>220.5332336425781</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0.09977585001332034</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>9.977585001332034</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H116"/>
+  <autoFilter ref="A1:H117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4453,7 +4487,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.622556209564209</v>
+        <v>2.622556447982788</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.68250560760498</v>
+        <v>2.682507038116455</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0228591470497912</v>
+        <v>0.0228595995254095</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.28591470497912</v>
+        <v>2.28595995254095</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.68250560760498</v>
+        <v>2.682507038116455</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.496466398239136</v>
+        <v>2.49646782875061</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935277556863939</v>
+        <v>-0.06935273858460167</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935277556863939</v>
+        <v>-6.935273858460167</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.496466398239136</v>
+        <v>2.49646782875061</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.67974066734314</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341347323291636</v>
+        <v>0.07341314465886306</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341347323291636</v>
+        <v>7.341314465886306</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.67974066734314</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565841436386108</v>
+        <v>2.565841197967529</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250382596535285</v>
+        <v>-0.04250417050352995</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250382596535285</v>
+        <v>-4.250417050352995</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565841436386108</v>
+        <v>2.565841197967529</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834127426147</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854459413790421</v>
+        <v>0.3854458842745316</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54459413790421</v>
+        <v>38.54458842745316</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834127426147</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454655740082078</v>
+        <v>0.001454723004039815</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1454655740082078</v>
+        <v>0.1454723004039815</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.002050876617432</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241696717852019</v>
+        <v>0.1241698810152463</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41696717852019</v>
+        <v>12.41698810152463</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.002050876617432</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.176387310028076</v>
+        <v>4.176388263702393</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356189773556429</v>
+        <v>0.04356201169344254</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356189773556429</v>
+        <v>4.356201169344254</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.176387310028076</v>
+        <v>4.176388263702393</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
         <v>4.40635347366333</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506341882685883</v>
+        <v>0.05506317790412329</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506341882685883</v>
+        <v>5.506317790412329</v>
       </c>
     </row>
     <row r="11">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097486972808838</v>
+        <v>5.097490310668945</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568493093612204</v>
+        <v>0.1568500668719666</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68493093612204</v>
+        <v>15.68500668719666</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097486972808838</v>
+        <v>5.097490310668945</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571060180664</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882105628470177</v>
+        <v>-0.02882187930417091</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882105628470177</v>
+        <v>-2.882187930417091</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571060180664</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772735595703125</v>
+        <v>4.772735118865967</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592239798838426</v>
+        <v>-0.03592230858882117</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592239798838426</v>
+        <v>-3.592230858882117</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772735595703125</v>
+        <v>4.772735118865967</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.062729358673096</v>
+        <v>6.062732696533203</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702839361416431</v>
+        <v>0.2702847624139151</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02839361416432</v>
+        <v>27.02847624139151</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.062729358673096</v>
+        <v>6.062732696533203</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484773445048615</v>
+        <v>-0.01484819817920868</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484773445048615</v>
+        <v>-1.484819817920868</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786457061768</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301657298715189</v>
+        <v>-0.04301656955288269</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301657298715189</v>
+        <v>-4.301656955288269</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786457061768</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.550673484802246</v>
+        <v>5.550672054290771</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888710249012416</v>
+        <v>-0.02888743377860092</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888710249012416</v>
+        <v>-2.888743377860092</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.550673484802246</v>
+        <v>5.550672054290771</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228055953979492</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220360864374244</v>
+        <v>0.1220366333256104</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20360864374244</v>
+        <v>12.20366333256104</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228055953979492</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850456237792969</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062882526693603</v>
+        <v>-0.06062896446669497</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062882526693603</v>
+        <v>-6.062896446669496</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850456237792969</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047036647796631</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360086837908227</v>
+        <v>0.03360053962341936</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360086837908227</v>
+        <v>3.360053962341936</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047036647796631</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935433864593506</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469144753935934</v>
+        <v>0.146914667857688</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.69144753935934</v>
+        <v>14.6914667857688</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935433864593506</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835258483887</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211166243223705</v>
+        <v>0.001211441341556485</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211166243223705</v>
+        <v>0.1211441341556485</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835258483887</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.209483623504639</v>
+        <v>5.209482192993164</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497683912712815</v>
+        <v>-0.249768751839513</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97683912712815</v>
+        <v>-24.9768751839513</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.209483623504639</v>
+        <v>5.209482192993164</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042298793792725</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240500045812026</v>
+        <v>-0.2240498830397153</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40500045812026</v>
+        <v>-22.40498830397153</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042298793792725</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.302005052566528</v>
+        <v>3.302004814147949</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.183136818674309</v>
+        <v>-0.1831367812965286</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.3136818674309</v>
+        <v>-18.31367812965286</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.302005052566528</v>
+        <v>3.302004814147949</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530071258545</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677904068510788</v>
+        <v>0.07677919063725391</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677904068510788</v>
+        <v>7.677919063725391</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530071258545</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417715072632</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421900381634172</v>
+        <v>0.07421899883953387</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421900381634172</v>
+        <v>7.421899883953387</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417715072632</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         <v>4.445836544036865</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640089866296075</v>
+        <v>0.1640089139689633</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40089866296075</v>
+        <v>16.40089139689633</v>
       </c>
     </row>
     <row r="29">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481488704681396</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019546108555708</v>
+        <v>0.008019224344257836</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019546108555708</v>
+        <v>0.8019224344257836</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481488704681396</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765674591064</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507479491647804</v>
+        <v>-0.2507477632008893</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07479491647804</v>
+        <v>-25.07477632008893</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765674591064</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070911407470703</v>
+        <v>4.070912837982178</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123869864642927</v>
+        <v>0.212387498580785</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23869864642927</v>
+        <v>21.2387498580785</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070911407470703</v>
+        <v>4.070912837982178</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>4.182209491729736</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733984435396586</v>
+        <v>0.02733948334858605</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733984435396586</v>
+        <v>2.733948334858605</v>
       </c>
     </row>
     <row r="33">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.156326770782471</v>
+        <v>4.156326293945312</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188767205097756</v>
+        <v>-0.006188881220705822</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188767205097756</v>
+        <v>-0.6188881220705822</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.156326770782471</v>
+        <v>4.156326293945312</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.319096088409424</v>
+        <v>4.319095134735107</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916181922248385</v>
+        <v>0.03916170898971694</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916181922248385</v>
+        <v>3.916170898971694</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.319096088409424</v>
+        <v>4.319095134735107</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987789630889893</v>
+        <v>4.987791061401367</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.154822566757649</v>
+        <v>0.1548231529536039</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.4822566757649</v>
+        <v>15.48231529536039</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987789630889893</v>
+        <v>4.987791061401367</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381811618804932</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899683685315129</v>
+        <v>0.07899700539838994</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899683685315129</v>
+        <v>7.899700539838994</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381811618804932</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842668533325195</v>
+        <v>5.842667579650879</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563278232560179</v>
+        <v>0.08563212417834198</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.56327823256018</v>
+        <v>8.563212417834198</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842668533325195</v>
+        <v>5.842667579650879</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1744,10 +1744,10 @@
         <v>5.870727062225342</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802348231823794</v>
+        <v>0.004802512241529833</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4802348231823794</v>
+        <v>0.4802512241529833</v>
       </c>
     </row>
     <row r="39">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710042476654053</v>
+        <v>6.710043430328369</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661787258361</v>
+        <v>0.1429663411715274</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29661787258361</v>
+        <v>14.29663411715274</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710042476654053</v>
+        <v>6.710043430328369</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395654513128542</v>
+        <v>-0.0239566127896278</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395654513128542</v>
+        <v>-2.39566127896278</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         <v>7.261864185333252</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012308531945</v>
+        <v>0.1088011501242385</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88012308531945</v>
+        <v>10.88011501242385</v>
       </c>
     </row>
     <row r="42">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443387031555176</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059699667439601</v>
+        <v>0.07059732102863103</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059699667439601</v>
+        <v>7.059732102863103</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443387031555176</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         <v>10.55399703979492</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176071683315141</v>
+        <v>0.1176068297349091</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76071683315141</v>
+        <v>11.76068297349091</v>
       </c>
     </row>
     <row r="45">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.32878017425537</v>
+        <v>13.328782081604</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921160074748678</v>
+        <v>0.06921175375168209</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921160074748678</v>
+        <v>6.921175375168209</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.32878017425537</v>
+        <v>13.328782081604</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799705505371</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556732179522692</v>
+        <v>-0.02556760433653082</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.556732179522692</v>
+        <v>-2.556760433653082</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799705505371</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998199561433103</v>
+        <v>-0.004998053440725236</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998199561433103</v>
+        <v>-0.4998053440725236</v>
       </c>
     </row>
     <row r="51">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.64411449432373</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579413045721027</v>
+        <v>0.05579390906862258</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579413045721027</v>
+        <v>5.579390906862258</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.64411449432373</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636960049531378</v>
+        <v>-0.02636918664632026</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636960049531378</v>
+        <v>-2.636918664632026</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93761920928955</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545437838092</v>
+        <v>0.1244544451908152</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44545437838092</v>
+        <v>12.44544451908152</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93761920928955</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         <v>16.16670608520508</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228130993934912</v>
+        <v>0.08228117174547189</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228130993934911</v>
+        <v>8.22811717454719</v>
       </c>
     </row>
     <row r="55">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.41006851196289</v>
+        <v>19.41006660461426</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517175579831477</v>
+        <v>-0.02517185159072888</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517175579831477</v>
+        <v>-2.517185159072888</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.41006851196289</v>
+        <v>19.41006660461426</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683471679688</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099974588429</v>
+        <v>0.1482103068206888</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82099974588429</v>
+        <v>14.82103068206888</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683471679688</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.62515830993652</v>
+        <v>20.62515258789062</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455865437939457</v>
+        <v>-0.07455906952685742</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455865437939457</v>
+        <v>-7.455906952685742</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.62515830993652</v>
+        <v>20.62515258789062</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341664229132356</v>
+        <v>0.2341669502622643</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41664229132356</v>
+        <v>23.41669502622643</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.53269577026367</v>
+        <v>32.53270721435547</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780535014795418</v>
+        <v>0.2780537595323853</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80535014795418</v>
+        <v>27.80537595323853</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.53269577026367</v>
+        <v>32.53270721435547</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         <v>29.28561019897461</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09980991413127971</v>
+        <v>-0.09981023079284457</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.98099141312797</v>
+        <v>-9.981023079284457</v>
       </c>
     </row>
     <row r="62">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.3816089630127</v>
+        <v>24.38160514831543</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542959030992</v>
+        <v>-0.1674544261615176</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74542959030993</v>
+        <v>-16.74544261615176</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.3816089630127</v>
+        <v>24.38160514831543</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28104019165039</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124858161063338</v>
+        <v>-0.004124624119425047</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124858161063338</v>
+        <v>-0.4124624119425047</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28104019165039</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.17429733276367</v>
+        <v>27.17430114746094</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571387757528</v>
+        <v>0.1191572079686052</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91571387757529</v>
+        <v>11.91572079686052</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.17429733276367</v>
+        <v>27.17430114746094</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>18.47107696533203</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202739802562728</v>
+        <v>-0.3202740756754329</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02739802562728</v>
+        <v>-32.02740756754329</v>
       </c>
     </row>
     <row r="66">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59556198120117</v>
+        <v>18.59556007385254</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739456291735557</v>
+        <v>0.006739353030370099</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739456291735557</v>
+        <v>0.6739353030370099</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59556198120117</v>
+        <v>18.59556007385254</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013675689697</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709377881579</v>
+        <v>-0.1879709570683575</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79709377881579</v>
+        <v>-18.79709570683575</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013675689697</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09246826171875</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981658545877099</v>
+        <v>0.1981662585587558</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81658545877099</v>
+        <v>19.81662585587558</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09246826171875</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538513183594</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689699318887956</v>
+        <v>-0.1689700016846472</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89699318887956</v>
+        <v>-16.89700016846471</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538513183594</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>12.09545421600342</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341276631157</v>
+        <v>-0.1955342297154857</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55341276631157</v>
+        <v>-19.55342297154857</v>
       </c>
     </row>
     <row r="71">
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.5653018951416</v>
+        <v>14.56530094146729</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415308901092</v>
+        <v>-0.1364415874322625</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64415308901092</v>
+        <v>-13.64415874322625</v>
       </c>
     </row>
     <row r="74">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.5653018951416</v>
+        <v>14.56530094146729</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47190284729004</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368691557148624</v>
+        <v>0.3368688503927728</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68691557148624</v>
+        <v>33.68688503927728</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47190284729004</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863563537598</v>
+        <v>23.13863754272461</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883089093471031</v>
+        <v>0.1883093564995657</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83089093471031</v>
+        <v>18.83093564995657</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863563537598</v>
+        <v>23.13863754272461</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68914222717285</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966627014446669</v>
+        <v>0.1966625203708421</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66627014446669</v>
+        <v>19.66625203708421</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68914222717285</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008053614069193</v>
+        <v>-0.001007915914793878</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1008053614069193</v>
+        <v>-0.1007915914793878</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71432876586914</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.363436428780211</v>
+        <v>0.3634364726737245</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.3436428780211</v>
+        <v>36.34364726737245</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71432876586914</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182106865009505</v>
+        <v>0.1182105733971262</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82106865009505</v>
+        <v>11.82105733971262</v>
       </c>
     </row>
     <row r="80">
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.20398330688477</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619655619364927</v>
+        <v>0.05619663807868869</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619655619364927</v>
+        <v>5.619663807868869</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.20398330688477</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36948013305664</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780952231065</v>
+        <v>-0.1185779309735295</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85780952231065</v>
+        <v>-11.85779309735295</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36948013305664</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.65856170654297</v>
+        <v>40.6585693359375</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.062507267540302</v>
+        <v>-0.06250733900434413</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.2507267540302</v>
+        <v>-6.250733900434414</v>
       </c>
     </row>
     <row r="84">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.65856170654297</v>
+        <v>40.6585693359375</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.63073348999023</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468859579084962</v>
+        <v>0.1468856488778802</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68859579084962</v>
+        <v>14.68856488778803</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.63073348999023</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.37887573242188</v>
+        <v>49.37887954711914</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893414142888309</v>
+        <v>0.05893430986310011</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893414142888309</v>
+        <v>5.893430986310011</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.37887573242188</v>
+        <v>49.37887954711914</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175564739466</v>
+        <v>0.2424175377463125</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24175564739466</v>
+        <v>24.24175377463125</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.88337707519531</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858097587910202</v>
+        <v>0.2858094301189487</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58097587910202</v>
+        <v>28.58094301189487</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.88337707519531</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
         <v>90.09909820556641</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421810468342366</v>
+        <v>0.1421812677718244</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21810468342366</v>
+        <v>14.21812677718244</v>
       </c>
     </row>
     <row r="89">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212738037109</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688708902152934</v>
+        <v>0.2688710673211081</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88708902152934</v>
+        <v>26.88710673211081</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212738037109</v>
+        <v>109.3212890625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269432152707823</v>
+        <v>0.1269429881861628</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69432152707823</v>
+        <v>12.69429881861628</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277657397651536</v>
+        <v>-0.05277645338988224</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277657397651536</v>
+        <v>-5.277645338988224</v>
       </c>
     </row>
     <row r="93">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008212771048568</v>
+        <v>0.02008206101966881</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008212771048568</v>
+        <v>2.008206101966881</v>
       </c>
     </row>
     <row r="94">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150207519531</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742808690201669</v>
+        <v>0.0174281509928309</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.742808690201669</v>
+        <v>1.74281509928309</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150207519531</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047546386719</v>
+        <v>132.4047393798828</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321497710709581</v>
+        <v>0.09321478225631852</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321497710709581</v>
+        <v>9.321478225631852</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047546386719</v>
+        <v>132.4047393798828</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3716,10 +3716,10 @@
         <v>137.8800354003906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135259928286272</v>
+        <v>0.04135271929200823</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135259928286272</v>
+        <v>4.135271929200823</v>
       </c>
     </row>
     <row r="97">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398651123047</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691133769347</v>
+        <v>-0.02857680067055435</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857691133769347</v>
+        <v>-2.857680067055435</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398651123047</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
         <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901794305278</v>
+        <v>-0.1058902812899192</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58901794305278</v>
+        <v>-10.58902812899192</v>
       </c>
     </row>
     <row r="99">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039318634820721</v>
+        <v>0.04039305893354816</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039318634820721</v>
+        <v>4.039305893354816</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323250437332495</v>
+        <v>-0.1323248762370933</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23250437332495</v>
+        <v>-13.23248762370933</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982481462220356</v>
+        <v>0.004982410538207693</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.4982481462220356</v>
+        <v>0.4982410538207693</v>
       </c>
     </row>
     <row r="102">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348754882812</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258305979143173</v>
+        <v>0.125830694731885</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58305979143173</v>
+        <v>12.5830694731885</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348754882812</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.0207454681313487</v>
+        <v>-0.02074546634730989</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.07454681313487</v>
+        <v>-2.074546634730989</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125119707459349</v>
+        <v>0.07125110299903326</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125119707459349</v>
+        <v>7.125110299903326</v>
       </c>
     </row>
     <row r="107">
@@ -4121,13 +4121,13 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258827644807442</v>
+        <v>-0.1258826889444383</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.58827644807442</v>
+        <v>-12.58826889444383</v>
       </c>
     </row>
     <row r="109">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373099736807707</v>
+        <v>0.05373090631056576</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>5.373099736807707</v>
+        <v>5.373090631056576</v>
       </c>
     </row>
     <row r="110">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293472316669725</v>
+        <v>-0.07293464314527709</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>-7.293472316669725</v>
+        <v>-7.293464314527709</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925888464382</v>
+        <v>-0.01569258749190239</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-1.56925888464382</v>
+        <v>-1.569258749190239</v>
       </c>
     </row>
     <row r="113">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234709050238</v>
+        <v>0.1443234582488593</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>14.43234709050238</v>
+        <v>14.43234582488593</v>
       </c>
     </row>
     <row r="114">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797470065579535</v>
+        <v>0.05797461957992356</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.797470065579535</v>
+        <v>5.797461957992356</v>
       </c>
     </row>
     <row r="115">

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.682507038116455</v>
+        <v>2.682506084442139</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0228595995254095</v>
+        <v>0.02285923588240113</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.28595995254095</v>
+        <v>2.285923588240113</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.682507038116455</v>
+        <v>2.682506084442139</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.49646782875061</v>
+        <v>2.496467113494873</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935273858460167</v>
+        <v>-0.06935267436157733</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935273858460167</v>
+        <v>-6.935267436157733</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.49646782875061</v>
+        <v>2.496467113494873</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.679741382598877</v>
+        <v>2.679741621017456</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341314465886306</v>
+        <v>0.07341354770182096</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341314465886306</v>
+        <v>7.341354770182096</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.679741382598877</v>
+        <v>2.679741621017456</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565841197967529</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250417050352995</v>
+        <v>-0.04250443363410483</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250417050352995</v>
+        <v>-4.250443363410483</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565841197967529</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834127426147</v>
+        <v>3.554833889007568</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854458842745316</v>
+        <v>0.3854460488262499</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54458842745316</v>
+        <v>38.54460488262499</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834127426147</v>
+        <v>3.554833889007568</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.56000542640686</v>
+        <v>3.560005903244019</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454723004039815</v>
+        <v>0.001454924308121219</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1454723004039815</v>
+        <v>0.1454924308121219</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.56000542640686</v>
+        <v>3.560005903244019</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.002050876617432</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241698810152463</v>
+        <v>0.1241695964979852</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41698810152463</v>
+        <v>12.41695964979852</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.002050876617432</v>
+        <v>4.002050399780273</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.176388263702393</v>
+        <v>4.176385402679443</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356201169344254</v>
+        <v>0.04356142114270756</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356201169344254</v>
+        <v>4.356142114270756</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.176388263702393</v>
+        <v>4.176385402679443</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.40635347366333</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506317790412329</v>
+        <v>0.05506412902187185</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506317790412329</v>
+        <v>5.506412902187185</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.40635347366333</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097490310668945</v>
+        <v>5.097488880157471</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568500668719666</v>
+        <v>0.1568494918456691</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68500668719666</v>
+        <v>15.68494918456691</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097490310668945</v>
+        <v>5.097488880157471</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         <v>4.950571060180664</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882187930417091</v>
+        <v>-0.02882160676185097</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882187930417091</v>
+        <v>-2.882160676185097</v>
       </c>
     </row>
     <row r="13">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772735118865967</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592230858882117</v>
+        <v>-0.03592211594956707</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592230858882117</v>
+        <v>-3.592211594956707</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772735118865967</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.062732696533203</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702847624139151</v>
+        <v>0.2702840090465197</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02847624139151</v>
+        <v>27.02840090465197</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.062732696533203</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.97271203994751</v>
+        <v>5.972712516784668</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484819817920868</v>
+        <v>-0.01484773211492074</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484819817920868</v>
+        <v>-1.484773211492074</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.97271203994751</v>
+        <v>5.972712516784668</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         <v>5.715786457061768</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301656955288269</v>
+        <v>-0.04301664595456089</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301656955288269</v>
+        <v>-4.301664595456089</v>
       </c>
     </row>
     <row r="17">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.550672054290771</v>
+        <v>5.550674438476562</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888743377860092</v>
+        <v>-0.02888701665563653</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888743377860092</v>
+        <v>-2.888701665563653</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.550672054290771</v>
+        <v>5.550674438476562</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220366333256104</v>
+        <v>0.1220359795639541</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20366333256104</v>
+        <v>12.20359795639541</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850456714630127</v>
+        <v>5.850455284118652</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062896446669497</v>
+        <v>-0.06062905031329091</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062896446669496</v>
+        <v>-6.062905031329091</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850456714630127</v>
+        <v>5.850455284118652</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047036170959473</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360053962341936</v>
+        <v>0.0336009553605936</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360053962341936</v>
+        <v>3.36009553605936</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047036170959473</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.146914667857688</v>
+        <v>0.1469146446878671</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.6914667857688</v>
+        <v>14.69146446878671</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>6.943835258483887</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211441341556485</v>
+        <v>0.001211303667462804</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211441341556485</v>
+        <v>0.1211303667462804</v>
       </c>
     </row>
     <row r="23">
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.209482192993164</v>
+        <v>5.20948314666748</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.249768751839513</v>
+        <v>-0.2497686144983635</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.9768751839513</v>
+        <v>-24.97686144983635</v>
       </c>
     </row>
     <row r="24">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.209482192993164</v>
+        <v>5.20948314666748</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042297840118408</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240498830397153</v>
+        <v>-0.224050116621593</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40498830397153</v>
+        <v>-22.4050116621593</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042297840118408</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.302004814147949</v>
+        <v>3.302005767822266</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831367812965286</v>
+        <v>-0.1831364490139741</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31367812965286</v>
+        <v>-18.31364490139741</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.302004814147949</v>
+        <v>3.302005767822266</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555530071258545</v>
+        <v>3.555530309677124</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677919063725391</v>
+        <v>0.07677895184963979</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677919063725391</v>
+        <v>7.677895184963979</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555530071258545</v>
+        <v>3.555530309677124</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819417238235474</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421899883953387</v>
+        <v>0.07421872563992093</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421899883953387</v>
+        <v>7.421872563992093</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819417238235474</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445836544036865</v>
+        <v>4.445834159851074</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640089139689633</v>
+        <v>0.1640085077232876</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40089139689633</v>
+        <v>16.40085077232876</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445836544036865</v>
+        <v>4.445834159851074</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481488704681396</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019224344257836</v>
+        <v>0.008020086683348415</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019224344257836</v>
+        <v>0.8020086683348415</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481488704681396</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507477632008893</v>
+        <v>-0.2507480555662548</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07477632008893</v>
+        <v>-25.07480555662548</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070912837982178</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.212387498580785</v>
+        <v>0.2123877266768006</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.2387498580785</v>
+        <v>21.23877266768006</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070912837982178</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182209491729736</v>
+        <v>4.182210445404053</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733948334858605</v>
+        <v>0.02733959727896007</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733948334858605</v>
+        <v>2.733959727896007</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182209491729736</v>
+        <v>4.182210445404053</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         <v>4.156326293945312</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188881220705822</v>
+        <v>-0.006189107840612107</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188881220705822</v>
+        <v>-0.6189107840612107</v>
       </c>
     </row>
     <row r="34">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.319095134735107</v>
+        <v>4.31909704208374</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916170898971694</v>
+        <v>0.03916216789224225</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916170898971694</v>
+        <v>3.916216789224225</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.319095134735107</v>
+        <v>4.31909704208374</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         <v>4.987791061401367</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548231529536039</v>
+        <v>0.1548226429742401</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48231529536039</v>
+        <v>15.48226429742401</v>
       </c>
     </row>
     <row r="36">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381811618804932</v>
+        <v>5.381809711456299</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899700539838994</v>
+        <v>0.07899662299491528</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899700539838994</v>
+        <v>7.899662299491528</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381811618804932</v>
+        <v>5.381809711456299</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         <v>5.842667579650879</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563212417834198</v>
+        <v>0.08563250893348173</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563212417834198</v>
+        <v>8.563250893348172</v>
       </c>
     </row>
     <row r="38">
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802512241529833</v>
+        <v>0.004802349015690988</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4802512241529833</v>
+        <v>0.4802349015690988</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         <v>6.710043430328369</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429663411715274</v>
+        <v>0.142966526841515</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29663411715274</v>
+        <v>14.2966526841515</v>
       </c>
     </row>
     <row r="40">
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.0239566127896278</v>
+        <v>-0.02395668385282779</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.39566127896278</v>
+        <v>-2.395668385282779</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.261864185333252</v>
+        <v>7.261863708496094</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088011501242385</v>
+        <v>0.1088011580457702</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88011501242385</v>
+        <v>10.88011580457702</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.261864185333252</v>
+        <v>7.261863708496094</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.820673942565918</v>
+        <v>8.820672988891602</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.214656969264309</v>
+        <v>0.2146569176961779</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.4656969264309</v>
+        <v>21.46569176961779</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.820673942565918</v>
+        <v>8.820672988891602</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443391799926758</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059732102863103</v>
+        <v>0.07059765301574861</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059732102863103</v>
+        <v>7.059765301574861</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443391799926758</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399703979492</v>
+        <v>10.55399608612061</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176068297349091</v>
+        <v>0.1176065030154168</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76068297349091</v>
+        <v>11.76065030154168</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399703979492</v>
+        <v>10.55399608612061</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.29794979095459</v>
+        <v>13.29795074462891</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599918060250836</v>
+        <v>0.2599920102412046</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99918060250836</v>
+        <v>25.99920102412046</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.29794979095459</v>
+        <v>13.29795074462891</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.45708274841309</v>
+        <v>13.4570837020874</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196672870330273</v>
+        <v>0.01196672784509833</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196672870330273</v>
+        <v>1.196672784509833</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.45708274841309</v>
+        <v>13.4570837020874</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         <v>12.465989112854</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364847598012692</v>
+        <v>-0.07364854162864898</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364847598012691</v>
+        <v>-7.364854162864898</v>
       </c>
     </row>
     <row r="48">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32878112792969</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921175375168209</v>
+        <v>0.06921167724958432</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921175375168209</v>
+        <v>6.921167724958432</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32878112792969</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799705505371</v>
+        <v>12.98799991607666</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556760433653082</v>
+        <v>-0.0255673199658849</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.556760433653082</v>
+        <v>-2.55673199658849</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799705505371</v>
+        <v>12.98799991607666</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308139801025</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998053440725236</v>
+        <v>-0.004998346049113311</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998053440725236</v>
+        <v>-0.4998346049113311</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308139801025</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
         <v>13.64411163330078</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579390906862258</v>
+        <v>0.05579398698220239</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579390906862258</v>
+        <v>5.579398698220239</v>
       </c>
     </row>
     <row r="52">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432750701904</v>
+        <v>13.28432559967041</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636918664632026</v>
+        <v>-0.02636932643912504</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636918664632026</v>
+        <v>-2.636932643912504</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432750701904</v>
+        <v>13.28432559967041</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762016296387</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544451908152</v>
+        <v>0.1244545348492871</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44544451908152</v>
+        <v>12.44545348492871</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762016296387</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228117174547189</v>
+        <v>0.08228136852999035</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.22811717454719</v>
+        <v>8.228136852999036</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.91127014160156</v>
+        <v>19.9112720489502</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316219541977889</v>
+        <v>0.2316219268710247</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16219541977889</v>
+        <v>23.16219268710247</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.91127014160156</v>
+        <v>19.9112720489502</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.41006660461426</v>
+        <v>19.41007041931152</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517185159072888</v>
+        <v>-0.0251717533870518</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.517185159072888</v>
+        <v>-2.51717533870518</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.41006660461426</v>
+        <v>19.41007041931152</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683853149414</v>
+        <v>22.28683662414551</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482103068206888</v>
+        <v>0.1482099828948495</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82103068206888</v>
+        <v>14.82099828948495</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683853149414</v>
+        <v>22.28683662414551</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
         <v>20.62515258789062</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455906952685742</v>
+        <v>-0.07455899032591362</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455906952685742</v>
+        <v>-7.455899032591362</v>
       </c>
     </row>
     <row r="59">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341669502622643</v>
+        <v>0.2341667653086137</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41669502622643</v>
+        <v>23.41667653086137</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.53270721435547</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537595323853</v>
+        <v>0.2780538012018414</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80537595323853</v>
+        <v>27.80538012018414</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.53270721435547</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981023079284457</v>
+        <v>-0.09981006661035974</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.981023079284457</v>
+        <v>-9.981006661035973</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.38160514831543</v>
+        <v>24.38160705566406</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674544261615176</v>
+        <v>-0.1674544152553439</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74544261615176</v>
+        <v>-16.74544152553439</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.38160514831543</v>
+        <v>24.38160705566406</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28104019165039</v>
+        <v>24.28103256225586</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124624119425047</v>
+        <v>-0.004125014941738225</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124624119425047</v>
+        <v>-0.4125014941738225</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28104019165039</v>
+        <v>24.28103256225586</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.17430114746094</v>
+        <v>27.1742992401123</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572079686052</v>
+        <v>0.1191574810683276</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91572079686052</v>
+        <v>11.91574810683276</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.17430114746094</v>
+        <v>27.1742992401123</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.47107696533203</v>
+        <v>18.47107315063477</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740756754329</v>
+        <v>-0.3202741683447206</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02740756754329</v>
+        <v>-32.02741683447206</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.47107696533203</v>
+        <v>18.47107315063477</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59556007385254</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739353030370099</v>
+        <v>0.006739767467747848</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739353030370099</v>
+        <v>0.6739767467747848</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59556007385254</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013198852539</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709570683575</v>
+        <v>-0.1879712775032717</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79709570683575</v>
+        <v>-18.79712775032717</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013198852539</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09247016906738</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981662585587558</v>
+        <v>0.1981663592620166</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81662585587558</v>
+        <v>19.81663592620166</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09247016906738</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.03538608551025</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689700016846472</v>
+        <v>-0.168969966786725</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89700016846471</v>
+        <v>-16.8969966786725</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.03538608551025</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.09545421600342</v>
+        <v>12.09545516967773</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955342297154857</v>
+        <v>-0.195534115260649</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55342297154857</v>
+        <v>-19.5534115260649</v>
       </c>
     </row>
     <row r="71">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.09545421600342</v>
+        <v>12.09545516967773</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         <v>13.44858360290527</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118709031291722</v>
+        <v>0.1118708154629613</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18709031291722</v>
+        <v>11.18708154629613</v>
       </c>
     </row>
     <row r="72">
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.86660766601562</v>
+        <v>16.86660385131836</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.254154947765054</v>
+        <v>0.2541546641145687</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.4154947765054</v>
+        <v>25.41546641145687</v>
       </c>
     </row>
     <row r="73">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.86660766601562</v>
+        <v>16.86660385131836</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         <v>14.56530094146729</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415874322625</v>
+        <v>-0.1364413921224097</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64415874322625</v>
+        <v>-13.64413921224097</v>
       </c>
     </row>
     <row r="74">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368688503927728</v>
+        <v>0.3368689813443158</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68688503927728</v>
+        <v>33.68689813443157</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3002,10 +3002,10 @@
         <v>23.13863754272461</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883093564995657</v>
+        <v>0.1883092401000188</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83093564995657</v>
+        <v>18.83092401000188</v>
       </c>
     </row>
     <row r="76">
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68914031982422</v>
+        <v>27.68913841247559</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625203708421</v>
+        <v>0.1966624379395134</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66625203708421</v>
+        <v>19.66624379395135</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68914031982422</v>
+        <v>27.68913841247559</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3070,10 +3070,10 @@
         <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007915914793878</v>
+        <v>-0.00100784709986157</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1007915914793878</v>
+        <v>-0.100784709986157</v>
       </c>
     </row>
     <row r="78">
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432495117188</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364726737245</v>
+        <v>0.3634361968582969</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34364726737245</v>
+        <v>36.34361968582969</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432495117188</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105733971262</v>
+        <v>0.118210698457627</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82105733971262</v>
+        <v>11.8210698457627</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
         <v>46.58600997924805</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046520284189869</v>
+        <v>0.1046521283397153</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46520284189869</v>
+        <v>10.46521283397153</v>
       </c>
     </row>
     <row r="81">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36948013305664</v>
+        <v>43.36947250366211</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779309735295</v>
+        <v>-0.1185780860299585</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85779309735295</v>
+        <v>-11.85780860299585</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36948013305664</v>
+        <v>43.36947250366211</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3271,13 +3271,13 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.6585693359375</v>
+        <v>40.65856552124023</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250733900434413</v>
+        <v>-0.06250726204228019</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250733900434414</v>
+        <v>-6.250726204228019</v>
       </c>
     </row>
     <row r="84">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.6585693359375</v>
+        <v>40.65856552124023</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307258605957</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468856488778802</v>
+        <v>0.1468856626590918</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68856488778803</v>
+        <v>14.68856626590918</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307258605957</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         <v>49.37887954711914</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893430986310011</v>
+        <v>0.05893439649082755</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893430986310011</v>
+        <v>5.893439649082755</v>
       </c>
     </row>
     <row r="86">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34917831420898</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175377463125</v>
+        <v>0.2424173832390697</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24175377463125</v>
+        <v>24.24173832390697</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34917831420898</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858094301189487</v>
+        <v>0.285809590022434</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58094301189487</v>
+        <v>28.5809590022434</v>
       </c>
     </row>
     <row r="88">
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09909057617188</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421812677718244</v>
+        <v>0.1421811710544132</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21812677718244</v>
+        <v>14.21811710544132</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09909057617188</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.15634155273438</v>
+        <v>86.15633392333984</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376022325813289</v>
+        <v>-0.04376022696365323</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376022325813289</v>
+        <v>-4.376022696365323</v>
       </c>
     </row>
     <row r="90">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.15634155273438</v>
+        <v>86.15633392333984</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710673211081</v>
+        <v>0.2688710911304248</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88710673211081</v>
+        <v>26.88710911304248</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429881861628</v>
+        <v>0.1269431366228349</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69429881861628</v>
+        <v>12.69431366228348</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3580,10 +3580,10 @@
         <v>116.6968612670898</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277645338988224</v>
+        <v>-0.05277651204904255</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277645338988224</v>
+        <v>-5.277651204904254</v>
       </c>
     </row>
     <row r="93">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174281509928309</v>
+        <v>0.01742821508364489</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.74281509928309</v>
+        <v>1.742821508364489</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047393798828</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321478225631852</v>
+        <v>0.09321458740556565</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321478225631852</v>
+        <v>9.321458740556565</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047393798828</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>137.8800354003906</v>
+        <v>137.8800201416016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135271929200823</v>
+        <v>0.04135272405764212</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135271929200823</v>
+        <v>4.135272405764212</v>
       </c>
     </row>
     <row r="97">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>137.8800354003906</v>
+        <v>137.8800201416016</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398651123047</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680067055435</v>
+        <v>-0.02857680383306749</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857680067055435</v>
+        <v>-2.857680383306749</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398651123047</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
         <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902812899192</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58902812899192</v>
+        <v>-10.58901794305278</v>
       </c>
     </row>
     <row r="99">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942840576172</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039305893354816</v>
+        <v>0.04039318634820721</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039305893354816</v>
+        <v>4.039318634820721</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942840576172</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>108.1073608398438</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323248762370933</v>
+        <v>-0.1323249824993521</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23248762370933</v>
+        <v>-13.23249824993521</v>
       </c>
     </row>
     <row r="101">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406354069759602</v>
+        <v>0.24063554742098</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.06354069759602</v>
+        <v>24.063554742098</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.603515625</v>
+        <v>157.6035003662109</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516823827925</v>
+        <v>0.169251436814627</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92516823827926</v>
+        <v>16.9251436814627</v>
       </c>
     </row>
     <row r="104">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.603515625</v>
+        <v>157.6035003662109</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
         <v>177.4348754882812</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.125830694731885</v>
+        <v>0.1258308037320852</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.5830694731885</v>
+        <v>12.58308037320852</v>
       </c>
     </row>
     <row r="105">
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074546634730989</v>
+        <v>-0.02074555234387065</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074546634730989</v>
+        <v>-2.074555234387065</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125110299903326</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125110299903326</v>
+        <v>7.125119707459349</v>
       </c>
     </row>
     <row r="107">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.08527167560685012</v>
+        <v>0.08527175758426342</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>8.527167560685012</v>
+        <v>8.527175758426342</v>
       </c>
     </row>
     <row r="108">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258826889444383</v>
+        <v>-0.1258827549720258</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.58826889444383</v>
+        <v>-12.58827549720258</v>
       </c>
     </row>
     <row r="109">

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Returns'!$A$1:$H$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Source and Method'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.682506084442139</v>
+        <v>2.682506799697876</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285923588240113</v>
+        <v>0.02285950861465746</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285923588240113</v>
+        <v>2.285950861465746</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.682506084442139</v>
+        <v>2.682506799697876</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>2.496467113494873</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935267436157733</v>
+        <v>-0.06935292250664793</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935267436157733</v>
+        <v>-6.935292250664792</v>
       </c>
     </row>
     <row r="4">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.679741621017456</v>
+        <v>2.679741144180298</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341354770182096</v>
+        <v>0.0734133566970383</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341354770182096</v>
+        <v>7.34133566970383</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.679741621017456</v>
+        <v>2.679741144180298</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         <v>2.565840721130371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250443363410483</v>
+        <v>-0.04250426325590773</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250443363410483</v>
+        <v>-4.250426325590773</v>
       </c>
     </row>
     <row r="6">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554833889007568</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854460488262499</v>
+        <v>0.3854463275870208</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54460488262499</v>
+        <v>38.54463275870208</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554833889007568</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560005903244019</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454924308121219</v>
+        <v>0.001454655740082078</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1454924308121219</v>
+        <v>0.1454655740082078</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560005903244019</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.00205135345459</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241695964979852</v>
+        <v>0.1241699396708196</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41695964979852</v>
+        <v>12.41699396708196</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.002050399780273</v>
+        <v>4.00205135345459</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -758,10 +758,10 @@
         <v>4.176385402679443</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356142114270756</v>
+        <v>0.04356117246580737</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356142114270756</v>
+        <v>4.356117246580737</v>
       </c>
     </row>
     <row r="10">
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406353950500488</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506412902187185</v>
+        <v>0.05506401484726586</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506412902187185</v>
+        <v>5.506401484726586</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406353950500488</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         <v>5.097488880157471</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568494918456691</v>
+        <v>0.1568496170350731</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68494918456691</v>
+        <v>15.68496170350731</v>
       </c>
     </row>
     <row r="12">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.950571060180664</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882160676185097</v>
+        <v>-0.0288214196747697</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882160676185097</v>
+        <v>-2.88214196747697</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.950571060180664</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772733688354492</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592211594956707</v>
+        <v>-0.03592278326681819</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592211594956707</v>
+        <v>-3.592278326681819</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772733688354492</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.062730312347412</v>
+        <v>6.06273078918457</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840090465197</v>
+        <v>0.2702847435166309</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02840090465197</v>
+        <v>27.02847435166309</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.062730312347412</v>
+        <v>6.06273078918457</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.972712516784668</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484773211492074</v>
+        <v>-0.01484796689881163</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484773211492074</v>
+        <v>-1.484796689881163</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.972712516784668</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715786457061768</v>
+        <v>5.715785503387451</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301664595456089</v>
+        <v>-0.04301665282311129</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301664595456089</v>
+        <v>-4.301665282311129</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715786457061768</v>
+        <v>5.715785503387451</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.550674438476562</v>
+        <v>5.55067253112793</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888701665563653</v>
+        <v>-0.02888718832462622</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888701665563653</v>
+        <v>-2.888718832462622</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.550674438476562</v>
+        <v>5.55067253112793</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.22805643081665</v>
+        <v>6.228055000305176</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220359795639541</v>
+        <v>0.122036107404736</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20359795639541</v>
+        <v>12.2036107404736</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.22805643081665</v>
+        <v>6.228055000305176</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850455284118652</v>
+        <v>5.850455760955811</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062905031329091</v>
+        <v>-0.0606287579879855</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062905031329091</v>
+        <v>-6.062875798798551</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850455284118652</v>
+        <v>5.850455760955811</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         <v>6.047036170959473</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.0336009553605936</v>
+        <v>0.03360087111769672</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.36009553605936</v>
+        <v>3.360087111769672</v>
       </c>
     </row>
     <row r="21">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935434341430664</v>
+        <v>6.935434818267822</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469146446878671</v>
+        <v>0.1469147235425563</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.69146446878671</v>
+        <v>14.69147235425563</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935434341430664</v>
+        <v>6.935434818267822</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.943835258483887</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211303667462804</v>
+        <v>0.001211028569177319</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211303667462804</v>
+        <v>0.1211028569177319</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.943835258483887</v>
+        <v>6.943833827972412</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>5.20948314666748</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497686144983635</v>
+        <v>-0.2497684599418704</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97686144983635</v>
+        <v>-24.97684599418704</v>
       </c>
     </row>
     <row r="24">
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042297840118408</v>
+        <v>4.042296886444092</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.224050116621593</v>
+        <v>-0.2240502996866476</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.4050116621593</v>
+        <v>-22.40502996866476</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042297840118408</v>
+        <v>4.042296886444092</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         <v>3.302005767822266</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831364490139741</v>
+        <v>-0.1831362562963657</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31364490139741</v>
+        <v>-18.31362562963657</v>
       </c>
     </row>
     <row r="26">
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555530309677124</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677895184963979</v>
+        <v>0.07677880744130383</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677895184963979</v>
+        <v>7.677880744130383</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555530309677124</v>
+        <v>3.555529832839966</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417238235474</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421872563992093</v>
+        <v>0.07421907087205204</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421872563992093</v>
+        <v>7.421907087205204</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417238235474</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445834159851074</v>
+        <v>4.445835590362549</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640085077232876</v>
+        <v>0.1640086642779561</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40085077232876</v>
+        <v>16.40086642779561</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445834159851074</v>
+        <v>4.445835590362549</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481491088867188</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008020086683348415</v>
+        <v>0.008019976847981169</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8020086683348415</v>
+        <v>0.8019976847981169</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481491088867188</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765197753906</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480555662548</v>
+        <v>-0.2507481618085182</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07480555662548</v>
+        <v>-25.07481618085182</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765197753906</v>
+        <v>3.357765436172485</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123877266768006</v>
+        <v>0.2123872145602557</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23877266768006</v>
+        <v>21.23872145602557</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182210445404053</v>
+        <v>4.182209968566895</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733959727896007</v>
+        <v>0.0273398411515744</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733959727896007</v>
+        <v>2.73398411515744</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182210445404053</v>
+        <v>4.182209968566895</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         <v>4.156326293945312</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189107840612107</v>
+        <v>-0.006188994530671899</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6189107840612107</v>
+        <v>-0.6188994530671899</v>
       </c>
     </row>
     <row r="34">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.31909704208374</v>
+        <v>4.319095611572266</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916216789224225</v>
+        <v>0.03916182371534838</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916216789224225</v>
+        <v>3.916182371534838</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.31909704208374</v>
+        <v>4.319095611572266</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987791061401367</v>
+        <v>4.987790584564209</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548226429742401</v>
+        <v>0.1548229150566363</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48226429742401</v>
+        <v>15.48229150566362</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987791061401367</v>
+        <v>4.987790584564209</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381809711456299</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899662299491528</v>
+        <v>0.07899691734969516</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899662299491528</v>
+        <v>7.899691734969516</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381809711456299</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842667579650879</v>
+        <v>5.842669486999512</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563250893348173</v>
+        <v>0.08563267096236871</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563250893348172</v>
+        <v>8.563267096236871</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842667579650879</v>
+        <v>5.842669486999512</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870726108551025</v>
+        <v>5.870726585388184</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802349015690988</v>
+        <v>0.00480210260927838</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4802349015690988</v>
+        <v>0.480210260927838</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870726108551025</v>
+        <v>5.870726585388184</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710043430328369</v>
+        <v>6.710044384002686</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.142966526841515</v>
+        <v>0.1429665964522182</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.2966526841515</v>
+        <v>14.29665964522182</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710043430328369</v>
+        <v>6.710044384002686</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
         <v>6.549293041229248</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395668385282779</v>
+        <v>-0.02395682257433085</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395668385282779</v>
+        <v>-2.395682257433085</v>
       </c>
     </row>
     <row r="41">
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.820672988891602</v>
+        <v>8.820675849914551</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146569176961779</v>
+        <v>0.2146573116753359</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46569176961779</v>
+        <v>21.46573116753359</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.820672988891602</v>
+        <v>8.820675849914551</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443391799926758</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059765301574861</v>
+        <v>0.07059708952683108</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059765301574861</v>
+        <v>7.059708952683108</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443391799926758</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399608612061</v>
+        <v>10.55399799346924</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176065030154168</v>
+        <v>0.117606930723466</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76065030154168</v>
+        <v>11.76069307234659</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399608612061</v>
+        <v>10.55399799346924</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
         <v>13.29795074462891</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599920102412046</v>
+        <v>0.2599917825318532</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99920102412046</v>
+        <v>25.99917825318532</v>
       </c>
     </row>
     <row r="46">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.4570837020874</v>
+        <v>13.45708179473877</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196672784509833</v>
+        <v>0.01196658441332676</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196672784509833</v>
+        <v>1.196658441332676</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.4570837020874</v>
+        <v>13.45708179473877</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         <v>12.465989112854</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364854162864898</v>
+        <v>-0.07364841033159564</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364854162864898</v>
+        <v>-7.364841033159564</v>
       </c>
     </row>
     <row r="48">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.32878112792969</v>
+        <v>13.328782081604</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921167724958432</v>
+        <v>0.06921175375168209</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921167724958432</v>
+        <v>6.921175375168209</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.32878112792969</v>
+        <v>13.328782081604</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799991607666</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255673199658849</v>
+        <v>-0.02556746123653708</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.55673199658849</v>
+        <v>-2.556746123653708</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799991607666</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.92308139801025</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998346049113311</v>
+        <v>-0.004998199561433103</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998346049113311</v>
+        <v>-0.4998199561433103</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.92308139801025</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.64411163330078</v>
+        <v>13.6441125869751</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579398698220239</v>
+        <v>0.0557939828648184</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579398698220239</v>
+        <v>5.57939828648184</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.64411163330078</v>
+        <v>13.6441125869751</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432559967041</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636932643912504</v>
+        <v>-0.02636946438879895</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636932643912504</v>
+        <v>-2.636946438879895</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432559967041</v>
+        <v>13.28432464599609</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762016296387</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545348492871</v>
+        <v>0.1244546873627026</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44545348492871</v>
+        <v>12.44546873627026</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762016296387</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         <v>16.16670799255371</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228136852999035</v>
+        <v>0.08228129943304796</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228136852999036</v>
+        <v>8.228129943304797</v>
       </c>
     </row>
     <row r="55">
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.62515258789062</v>
+        <v>20.62515449523926</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455899032591362</v>
+        <v>-0.07455890474406701</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455899032591362</v>
+        <v>-7.455890474406701</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.62515258789062</v>
+        <v>20.62515449523926</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341667653086137</v>
+        <v>0.2341668361304334</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41667653086137</v>
+        <v>23.41668361304334</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53271102905273</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780538012018414</v>
+        <v>0.2780539093935128</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80538012018414</v>
+        <v>27.80539093935128</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53271102905273</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.28561210632324</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981006661035974</v>
+        <v>-0.09981033634665004</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.981006661035973</v>
+        <v>-9.981033634665003</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.28561210632324</v>
+        <v>29.28561019897461</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         <v>24.38160705566406</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674544152553439</v>
+        <v>-0.1674543610323084</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74544152553439</v>
+        <v>-16.74543610323084</v>
       </c>
     </row>
     <row r="63">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103256225586</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004125014941738225</v>
+        <v>-0.004124858483746885</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4125014941738225</v>
+        <v>-0.4124858483746885</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103256225586</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         <v>27.1742992401123</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191574810683276</v>
+        <v>0.119157305241937</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91574810683276</v>
+        <v>11.9157305241937</v>
       </c>
     </row>
     <row r="65">
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.47107315063477</v>
+        <v>18.47107124328613</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741683447206</v>
+        <v>-0.3202742385341527</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02741683447206</v>
+        <v>-32.02742385341527</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.47107315063477</v>
+        <v>18.47107124328613</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.5955638885498</v>
+        <v>18.59555816650391</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739767467747848</v>
+        <v>0.006739561640910274</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739767467747848</v>
+        <v>0.6739561640910274</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.5955638885498</v>
+        <v>18.59555816650391</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013198852539</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879712775032717</v>
+        <v>-0.1879708737784411</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79712775032717</v>
+        <v>-18.79708737784411</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013198852539</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247016906738</v>
+        <v>18.09247398376465</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981663592620166</v>
+        <v>0.1981663848721067</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81663592620166</v>
+        <v>19.81663848721067</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247016906738</v>
+        <v>18.09247398376465</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
         <v>15.03538608551025</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.168969966786725</v>
+        <v>-0.1689701420047741</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.8969966786725</v>
+        <v>-16.89701420047741</v>
       </c>
     </row>
     <row r="70">
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.44858360290527</v>
+        <v>13.44858264923096</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708154629613</v>
+        <v>0.1118707366172873</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18708154629613</v>
+        <v>11.18707366172873</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.44858360290527</v>
+        <v>13.44858264923096</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.86660385131836</v>
+        <v>16.86660575866699</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541546641145687</v>
+        <v>0.2541548948752226</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41546641145687</v>
+        <v>25.41548948752226</v>
       </c>
     </row>
     <row r="73">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.86660385131836</v>
+        <v>16.86660575866699</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.56530094146729</v>
+        <v>14.56530284881592</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364413921224097</v>
+        <v>-0.1364413766930278</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64413921224097</v>
+        <v>-13.64413766930278</v>
       </c>
     </row>
     <row r="74">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.56530094146729</v>
+        <v>14.56530284881592</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189903259277</v>
+        <v>19.47189521789551</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368689813443158</v>
+        <v>0.3368685443762311</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68689813443157</v>
+        <v>33.68685443762311</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189903259277</v>
+        <v>19.47189521789551</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863754272461</v>
+        <v>23.13863372802734</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883092401000188</v>
+        <v>0.1883092769912784</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83092401000188</v>
+        <v>18.83092769912784</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863754272461</v>
+        <v>23.13863372802734</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68913841247559</v>
+        <v>27.68914413452148</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966624379395134</v>
+        <v>0.1966628825185215</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66624379395135</v>
+        <v>19.66628825185215</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68913841247559</v>
+        <v>27.68914413452148</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3070,10 +3070,10 @@
         <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.00100784709986157</v>
+        <v>-0.001008053544630072</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.100784709986157</v>
+        <v>-0.1008053544630072</v>
       </c>
     </row>
     <row r="78">
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71432495117188</v>
+        <v>37.71433639526367</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634361968582969</v>
+        <v>0.3634366105814382</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34361968582969</v>
+        <v>36.34366105814382</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71432495117188</v>
+        <v>37.71433639526367</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.17256164550781</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.118210698457627</v>
+        <v>0.1182104602933247</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.8210698457627</v>
+        <v>11.82104602933247</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.17256164550781</v>
+        <v>42.17256546020508</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.58600997924805</v>
+        <v>46.58601760864258</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046521283397153</v>
+        <v>0.1046522093279367</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46521283397153</v>
+        <v>10.46522093279367</v>
       </c>
     </row>
     <row r="81">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.58600997924805</v>
+        <v>46.58601760864258</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.2039794921875</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619663807868869</v>
+        <v>0.05619630133525821</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619663807868869</v>
+        <v>5.619630133525821</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.2039794921875</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3240,10 +3240,10 @@
         <v>43.36947250366211</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780860299585</v>
+        <v>-0.1185779493598029</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85780860299585</v>
+        <v>-11.85779493598029</v>
       </c>
     </row>
     <row r="83">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.6307258605957</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468856626590918</v>
+        <v>0.1468857564818131</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68856626590918</v>
+        <v>14.68857564818131</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.6307258605957</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.37887954711914</v>
+        <v>49.37888336181641</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893439649082755</v>
+        <v>0.05893439166961034</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893439649082755</v>
+        <v>5.893439166961034</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.37887954711914</v>
+        <v>49.37888336181641</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34917831420898</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424173832390697</v>
+        <v>0.242417441765066</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24173832390697</v>
+        <v>24.2417441765066</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34917831420898</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.88336181640625</v>
+        <v>78.88335418701172</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.285809590022434</v>
+        <v>0.2858093057587894</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.5809590022434</v>
+        <v>28.58093057587894</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.88336181640625</v>
+        <v>78.88335418701172</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.09909057617188</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811710544132</v>
+        <v>0.1421813782406502</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21811710544132</v>
+        <v>14.21813782406502</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.09909057617188</v>
+        <v>90.09909820556641</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         <v>86.15633392333984</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376022696365323</v>
+        <v>-0.04376030793594532</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376022696365323</v>
+        <v>-4.376030793594532</v>
       </c>
     </row>
     <row r="90">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710911304248</v>
+        <v>0.2688711796833401</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88710911304248</v>
+        <v>26.88711796833401</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431366228349</v>
+        <v>0.1269429881861628</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69431366228348</v>
+        <v>12.69429881861628</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.1988677978516</v>
+        <v>123.198860168457</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968612670898</v>
+        <v>116.6968688964844</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277651204904255</v>
+        <v>-0.05277639146240565</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277651204904254</v>
+        <v>-5.277639146240565</v>
       </c>
     </row>
     <row r="93">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968612670898</v>
+        <v>116.6968688964844</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.0403747558594</v>
+        <v>119.0403671264648</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008206101966881</v>
+        <v>0.02008192895097527</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008206101966881</v>
+        <v>2.008192895097527</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.0403747558594</v>
+        <v>119.0403671264648</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150360107422</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742821508364489</v>
+        <v>0.0174282162006334</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.742821508364489</v>
+        <v>1.74282162006334</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150360107422</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321458740556565</v>
+        <v>0.09321453028446558</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321458740556565</v>
+        <v>9.321453028446559</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3716,10 +3716,10 @@
         <v>137.8800201416016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135272405764212</v>
+        <v>0.04135284406682982</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135272405764212</v>
+        <v>4.135284406682982</v>
       </c>
     </row>
     <row r="97">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398345947266</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680383306749</v>
+        <v>-0.02857691450021882</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857680383306749</v>
+        <v>-2.857691450021882</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398498535156</v>
+        <v>133.9398345947266</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.7569351196289</v>
+        <v>119.7569427490234</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901794305278</v>
+        <v>-0.1058900206097576</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58901794305278</v>
+        <v>-10.58900206097576</v>
       </c>
     </row>
     <row r="99">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.7569351196289</v>
+        <v>119.7569427490234</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942916870117</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039318634820721</v>
+        <v>0.0403930563602144</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039318634820721</v>
+        <v>4.03930563602144</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942916870117</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249824993521</v>
+        <v>-0.132324990602127</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249824993521</v>
+        <v>-13.2324990602127</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982410538207693</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.4982410538207693</v>
+        <v>0.4982481462220356</v>
       </c>
     </row>
     <row r="102">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.7900848388672</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.24063554742098</v>
+        <v>0.2406354069759602</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.063554742098</v>
+        <v>24.06354069759602</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.7900848388672</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         <v>157.6035003662109</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.169251436814627</v>
+        <v>0.1692515691786884</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.9251436814627</v>
+        <v>16.92515691786884</v>
       </c>
     </row>
     <row r="104">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348754882812</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258308037320852</v>
+        <v>0.1258307069145082</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58308037320852</v>
+        <v>12.58307069145081</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348754882812</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
         <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555234387065</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074555234387065</v>
+        <v>-2.07454681313487</v>
       </c>
     </row>
     <row r="106">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.08527175758426342</v>
+        <v>0.0852718395616765</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>8.527175758426342</v>
+        <v>8.527183956167651</v>
       </c>
     </row>
     <row r="108">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258827549720258</v>
+        <v>-0.1258828209996035</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.58827549720258</v>
+        <v>-12.58828209996035</v>
       </c>
     </row>
     <row r="109">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293464314527709</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>-7.293464314527709</v>
+        <v>-7.293472316669725</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.01569258749190239</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-1.569258749190239</v>
+        <v>-1.56925888464382</v>
       </c>
     </row>
     <row r="113">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234582488593</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>14.43234582488593</v>
+        <v>14.43234709050238</v>
       </c>
     </row>
     <row r="114">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797461957992356</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.797461957992356</v>
+        <v>5.797470065579535</v>
       </c>
     </row>
     <row r="115">
@@ -4436,8 +4436,42 @@
         <v>9.977585001332034</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Sept 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>220.5332336425781</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>228.3800048828125</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0.03558090139353665</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>3.558090139353665</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H117"/>
+  <autoFilter ref="A1:H118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4487,7 +4521,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.622556447982788</v>
+        <v>2.62255597114563</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.682506799697876</v>
+        <v>2.68250584602356</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285950861465746</v>
+        <v>0.02285933094947112</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285950861465746</v>
+        <v>2.285933094947112</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.682506799697876</v>
+        <v>2.68250584602356</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>2.496467113494873</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935292250664793</v>
+        <v>-0.06935259164652441</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935292250664792</v>
+        <v>-6.935259164652441</v>
       </c>
     </row>
     <row r="4">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.679741144180298</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0734133566970383</v>
+        <v>0.07341345219942963</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.34133566970383</v>
+        <v>7.341345219942963</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.679741144180298</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565840721130371</v>
+        <v>2.565840482711792</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250426325590773</v>
+        <v>-0.04250443741575582</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250426325590773</v>
+        <v>-4.250443741575582</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565840721130371</v>
+        <v>2.565840482711792</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834365844727</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854463275870208</v>
+        <v>0.3854463634027958</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54463275870208</v>
+        <v>38.54463634027958</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834604263306</v>
+        <v>3.554834365844727</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.560006141662598</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454655740082078</v>
+        <v>0.00145485704413173</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1454655740082078</v>
+        <v>0.145485704413173</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560005664825439</v>
+        <v>3.560006141662598</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.00205135345459</v>
+        <v>4.002051830291748</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699396708196</v>
+        <v>0.1241699230391513</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41699396708196</v>
+        <v>12.41699230391513</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.00205135345459</v>
+        <v>4.002051830291748</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.176385402679443</v>
+        <v>4.17638635635376</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356117246580737</v>
+        <v>0.0435612864237449</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.356117246580737</v>
+        <v>4.35612864237449</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.176385402679443</v>
+        <v>4.17638635635376</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.406353950500488</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506401484726586</v>
+        <v>0.05506388809886431</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506401484726586</v>
+        <v>5.506388809886431</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.406353950500488</v>
+        <v>4.406354427337646</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097488880157471</v>
+        <v>5.097488403320312</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568496170350731</v>
+        <v>0.1568493836298717</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68496170350731</v>
+        <v>15.68493836298717</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097488880157471</v>
+        <v>5.097488403320312</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571537017822</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.0288214196747697</v>
+        <v>-0.02882142237082763</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.88214196747697</v>
+        <v>-2.882142237082763</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950571537017822</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772733688354492</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592278326681819</v>
+        <v>-0.03592220880918029</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592278326681819</v>
+        <v>-3.592220880918029</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772733688354492</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.06273078918457</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702847435166309</v>
+        <v>0.2702840090465197</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02847435166309</v>
+        <v>27.02840090465197</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.06273078918457</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484796689881163</v>
+        <v>-0.01484781076548469</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-1.484796689881163</v>
+        <v>-1.484781076548469</v>
       </c>
     </row>
     <row r="16">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715785503387451</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301665282311129</v>
+        <v>-0.04301664938883587</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301665282311129</v>
+        <v>-4.301664938883587</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715785503387451</v>
+        <v>5.715785980224609</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.55067253112793</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888718832462622</v>
+        <v>-0.02888710249012416</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888718832462622</v>
+        <v>-2.888710249012416</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.55067253112793</v>
+        <v>5.550673484802246</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228055000305176</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.122036107404736</v>
+        <v>0.1220363441559658</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.2036107404736</v>
+        <v>12.20363441559658</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228055000305176</v>
+        <v>6.228057384490967</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850455760955811</v>
+        <v>5.850457191467285</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.0606287579879855</v>
+        <v>-0.06062888790395171</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062875798798551</v>
+        <v>-6.062888790395171</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850455760955811</v>
+        <v>5.850457191467285</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047036170959473</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360087111769672</v>
+        <v>0.03360045538057688</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360087111769672</v>
+        <v>3.360045538057688</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047036170959473</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935434818267822</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469147235425563</v>
+        <v>0.146914667857688</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.69147235425563</v>
+        <v>14.6914667857688</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935434818267822</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>6.943833827972412</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211028569177319</v>
+        <v>0.001211235080261108</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211028569177319</v>
+        <v>0.1211235080261108</v>
       </c>
     </row>
     <row r="23">
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042296886444092</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240502996866476</v>
+        <v>-0.2240500250890657</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40502996866476</v>
+        <v>-22.40500250890657</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042296886444092</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.302005767822266</v>
+        <v>3.30200457572937</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831362562963657</v>
+        <v>-0.1831368402774747</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31362562963657</v>
+        <v>-18.31368402774747</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.302005767822266</v>
+        <v>3.30200457572937</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         <v>3.555529832839966</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677880744130383</v>
+        <v>0.07677919618103357</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677880744130383</v>
+        <v>7.677919618103357</v>
       </c>
     </row>
     <row r="27">
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819418430328369</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421907087205204</v>
+        <v>0.07421920498347312</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421907087205204</v>
+        <v>7.421920498347312</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819417953491211</v>
+        <v>3.819418430328369</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445835590362549</v>
+        <v>4.445837020874023</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640086642779561</v>
+        <v>0.1640088934931905</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40086642779561</v>
+        <v>16.40088934931905</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445835590362549</v>
+        <v>4.445837020874023</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.481491088867188</v>
+        <v>4.481489658355713</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019976847981169</v>
+        <v>0.008019330738912256</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019976847981169</v>
+        <v>0.8019330738912256</v>
       </c>
     </row>
     <row r="30">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.481491088867188</v>
+        <v>4.481489658355713</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357764720916748</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507481618085182</v>
+        <v>-0.2507480822462205</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07481618085182</v>
+        <v>-25.07480822462205</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357765436172485</v>
+        <v>3.357764720916748</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070911884307861</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123872145602557</v>
+        <v>0.2123878988483392</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23872145602557</v>
+        <v>21.23878988483392</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070911884307861</v>
+        <v>4.070913314819336</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182209968566895</v>
+        <v>4.182210922241211</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.0273398411515744</v>
+        <v>0.02733971441168226</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.73398411515744</v>
+        <v>2.733971441168226</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182209968566895</v>
+        <v>4.182210922241211</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.156326293945312</v>
+        <v>4.156324863433838</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188994530671899</v>
+        <v>-0.006189563197233738</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6188994530671899</v>
+        <v>-0.6189563197233738</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.156326293945312</v>
+        <v>4.156324863433838</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
         <v>4.319095611572266</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916182371534838</v>
+        <v>0.03916218137096039</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916182371534838</v>
+        <v>3.916218137096039</v>
       </c>
     </row>
     <row r="35">
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987790584564209</v>
+        <v>4.987790107727051</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548229150566363</v>
+        <v>0.1548228046545519</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48229150566362</v>
+        <v>15.48228046545519</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987790584564209</v>
+        <v>4.987790107727051</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381810665130615</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899691734969516</v>
+        <v>0.07899673370009652</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899691734969516</v>
+        <v>7.899673370009652</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381810665130615</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842669486999512</v>
+        <v>5.842668056488037</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563267096236871</v>
+        <v>0.08563269372395554</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563267096236871</v>
+        <v>8.563269372395554</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842669486999512</v>
+        <v>5.842668056488037</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870726585388184</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480210260927838</v>
+        <v>0.004802430236670041</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.480210260927838</v>
+        <v>0.4802430236670041</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870726585388184</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710044384002686</v>
+        <v>6.710042953491211</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429665964522182</v>
+        <v>0.1429662599486818</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29665964522182</v>
+        <v>14.29662599486818</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710044384002686</v>
+        <v>6.710042953491211</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395682257433085</v>
+        <v>-0.02395654342885645</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395682257433085</v>
+        <v>-2.395654342885645</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549293518066406</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.261863708496094</v>
+        <v>7.261862754821777</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088011580457702</v>
+        <v>0.1088009317019811</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88011580457702</v>
+        <v>10.88009317019811</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.261863708496094</v>
+        <v>7.261862754821777</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.820675849914551</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146573116753359</v>
+        <v>0.2146572085391054</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46573116753359</v>
+        <v>21.46572085391054</v>
       </c>
     </row>
     <row r="43">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.820675849914551</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
         <v>9.443389892578125</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059708952683108</v>
+        <v>0.07059732102863103</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059708952683108</v>
+        <v>7.059732102863103</v>
       </c>
     </row>
     <row r="44">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399799346924</v>
+        <v>10.55399513244629</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.117606930723466</v>
+        <v>0.1176066277577954</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76069307234659</v>
+        <v>11.76066277577954</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399799346924</v>
+        <v>10.55399513244629</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.29795074462891</v>
+        <v>13.29794883728027</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599917825318532</v>
+        <v>0.2599919433730087</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99917825318532</v>
+        <v>25.99919433730087</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.29795074462891</v>
+        <v>13.29794883728027</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         <v>13.45708179473877</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196658441332676</v>
+        <v>0.01196672956150757</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196658441332676</v>
+        <v>1.196672956150757</v>
       </c>
     </row>
     <row r="47">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32877922058105</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921175375168209</v>
+        <v>0.06921152424538901</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921175375168209</v>
+        <v>6.921152424538901</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.328782081604</v>
+        <v>13.32877922058105</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799800872803</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556746123653708</v>
+        <v>-0.02556732362456904</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.556746123653708</v>
+        <v>-2.556732362456904</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98799800872803</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         <v>12.92308235168457</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998199561433103</v>
+        <v>-0.004998126501084554</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998199561433103</v>
+        <v>-0.4998126501084554</v>
       </c>
     </row>
     <row r="51">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.6441125869751</v>
+        <v>13.64411067962646</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.0557939828648184</v>
+        <v>0.05579383527242676</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.57939828648184</v>
+        <v>5.579383527242676</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.6441125869751</v>
+        <v>13.64411067962646</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
         <v>13.28432464599609</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636946438879895</v>
+        <v>-0.02636932828224614</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636946438879895</v>
+        <v>-2.636932828224614</v>
       </c>
     </row>
     <row r="53">
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762302398682</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244546873627026</v>
+        <v>0.124454830941596</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.44546873627026</v>
+        <v>12.4454830941596</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93762302398682</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.16670799255371</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228129943304796</v>
+        <v>0.08228103355163019</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228129943304797</v>
+        <v>8.228103355163018</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.16670799255371</v>
+        <v>16.16670608520508</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.9112720489502</v>
+        <v>19.91127586364746</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316219268710247</v>
+        <v>0.2316223081379092</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16219268710247</v>
+        <v>23.16223081379092</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.9112720489502</v>
+        <v>19.91127586364746</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.41007041931152</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.0251717533870518</v>
+        <v>-0.0251720359416866</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.51717533870518</v>
+        <v>-2.51720359416866</v>
       </c>
     </row>
     <row r="57">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.41007041931152</v>
+        <v>19.41006851196289</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683662414551</v>
+        <v>22.28683090209961</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099828948495</v>
+        <v>0.1482098009269623</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82099828948495</v>
+        <v>14.82098009269624</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683662414551</v>
+        <v>22.28683090209961</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
         <v>20.62515449523926</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455890474406701</v>
+        <v>-0.07455866714113257</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455890474406701</v>
+        <v>-7.455866714113258</v>
       </c>
     </row>
     <row r="59">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487976074219</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341668361304334</v>
+        <v>0.2341667436536166</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41668361304334</v>
+        <v>23.41667436536166</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487976074219</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.53271102905273</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780539093935128</v>
+        <v>0.2780537054365424</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80539093935128</v>
+        <v>27.80537054365424</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.53271102905273</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981033634665004</v>
+        <v>-0.09981006661035974</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.981033634665003</v>
+        <v>-9.981006661035973</v>
       </c>
     </row>
     <row r="62">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.28561019897461</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.38160705566406</v>
+        <v>24.38161087036133</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674543610323084</v>
+        <v>-0.167454284996934</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.74543610323084</v>
+        <v>-16.7454284996934</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.38160705566406</v>
+        <v>24.38161087036133</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103637695312</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124858483746885</v>
+        <v>-0.004124936067363305</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124858483746885</v>
+        <v>-0.4124936067363305</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103637695312</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.1742992401123</v>
+        <v>27.17429351806641</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.119157305241937</v>
+        <v>0.1191569816697338</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.9157305241937</v>
+        <v>11.91569816697338</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.1742992401123</v>
+        <v>27.17429351806641</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.47107124328613</v>
+        <v>18.4710750579834</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202742385341527</v>
+        <v>-0.320273955026533</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.02742385341527</v>
+        <v>-32.0273955026533</v>
       </c>
     </row>
     <row r="66">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.47107124328613</v>
+        <v>18.4710750579834</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59555816650391</v>
+        <v>18.59556579589844</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739561640910274</v>
+        <v>0.006739766771790112</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739561640910274</v>
+        <v>0.6739766771790112</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59555816650391</v>
+        <v>18.59556579589844</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013580322266</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879708737784411</v>
+        <v>-0.1879711556529652</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79708737784411</v>
+        <v>-18.79711556529652</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013580322266</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247398376465</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981663848721067</v>
+        <v>0.1981661828865631</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81663848721067</v>
+        <v>19.81661828865631</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247398376465</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538608551025</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689701420047741</v>
+        <v>-0.1689700016846472</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89701420047741</v>
+        <v>-16.89700016846471</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538608551025</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>12.09545516967773</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.195534115260649</v>
+        <v>-0.1955341662868347</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.5534115260649</v>
+        <v>-19.55341662868347</v>
       </c>
     </row>
     <row r="71">
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.44858264923096</v>
+        <v>13.44858455657959</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707366172873</v>
+        <v>0.1118708943086355</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18707366172873</v>
+        <v>11.18708943086355</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.44858264923096</v>
+        <v>13.44858455657959</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>16.86660575866699</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541548948752226</v>
+        <v>0.2541547170044127</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41548948752226</v>
+        <v>25.41547170044127</v>
       </c>
     </row>
     <row r="73">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189521789551</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368685443762311</v>
+        <v>0.336868675327757</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.68685443762311</v>
+        <v>33.6868675327757</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189521789551</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863372802734</v>
+        <v>23.13863945007324</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883092769912784</v>
+        <v>0.1883094544534847</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83092769912784</v>
+        <v>18.83094544534847</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863372802734</v>
+        <v>23.13863945007324</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.68914413452148</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966628825185215</v>
+        <v>0.1966624217283688</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66628825185215</v>
+        <v>19.66624217283688</v>
       </c>
     </row>
     <row r="77">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.68914413452148</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.66123199462891</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008053544630072</v>
+        <v>-0.001007984799151096</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1008053544630072</v>
+        <v>-0.1007984799151096</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.66123199462891</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71433639526367</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634366105814382</v>
+        <v>0.3634365666879342</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34366105814382</v>
+        <v>36.34365666879342</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71433639526367</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>42.17256546020508</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182104602933247</v>
+        <v>0.1182105733971262</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82104602933247</v>
+        <v>11.82105733971262</v>
       </c>
     </row>
     <row r="80">
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.2039794921875</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619630133525821</v>
+        <v>0.05619646510531018</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619630133525821</v>
+        <v>5.619646510531018</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.2039794921875</v>
+        <v>49.20398712158203</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36947250366211</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779493598029</v>
+        <v>-0.1185781635581729</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85779493598029</v>
+        <v>-11.85781635581728</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36947250366211</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         <v>40.65856552124023</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250726204228019</v>
+        <v>-0.06250717958217422</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250726204228019</v>
+        <v>-6.250717958217422</v>
       </c>
     </row>
     <row r="84">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.242417441765066</v>
+        <v>0.2424173645114505</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.2417441765066</v>
+        <v>24.24173645114504</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918594360352</v>
+        <v>61.34918212890625</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.88335418701172</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858093057587894</v>
+        <v>0.2858095100706863</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58093057587894</v>
+        <v>28.58095100706863</v>
       </c>
     </row>
     <row r="88">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.88335418701172</v>
+        <v>78.88336181640625</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09910583496094</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421813782406502</v>
+        <v>0.1421813644892354</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>14.21813782406502</v>
+        <v>14.21813644892353</v>
       </c>
     </row>
     <row r="89">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.09909820556641</v>
+        <v>90.09910583496094</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3478,10 +3478,10 @@
         <v>86.15633392333984</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376030793594532</v>
+        <v>-0.04376038890822365</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376030793594532</v>
+        <v>-4.376038890822365</v>
       </c>
     </row>
     <row r="90">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711796833401</v>
+        <v>0.2688710911304248</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88711796833401</v>
+        <v>26.88710911304248</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212814331055</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429881861628</v>
+        <v>0.1269431366228349</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69429881861628</v>
+        <v>12.69431366228348</v>
       </c>
     </row>
     <row r="92">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.198860168457</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968688964844</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277639146240565</v>
+        <v>-0.05277657397651536</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277639146240565</v>
+        <v>-5.277657397651536</v>
       </c>
     </row>
     <row r="93">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968688964844</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.0403671264648</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008192895097527</v>
+        <v>0.02008212771048568</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008192895097527</v>
+        <v>2.008212771048568</v>
       </c>
     </row>
     <row r="94">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.0403671264648</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         <v>121.1150283813477</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174282162006334</v>
+        <v>0.0174281509928309</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.74282162006334</v>
+        <v>1.74281509928309</v>
       </c>
     </row>
     <row r="95">
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047088623047</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321453028446558</v>
+        <v>0.09321465627039194</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321453028446559</v>
+        <v>9.321465627039194</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047088623047</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>137.8800201416016</v>
+        <v>137.8800506591797</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135284406682982</v>
+        <v>0.0413529545447211</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.135284406682982</v>
+        <v>4.13529545447211</v>
       </c>
     </row>
     <row r="97">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>137.8800201416016</v>
+        <v>137.8800506591797</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>133.9398345947266</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691450021882</v>
+        <v>-0.02857701884229569</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857691450021882</v>
+        <v>-2.857701884229569</v>
       </c>
     </row>
     <row r="98">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133.9398345947266</v>
+        <v>133.9398498535156</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
         <v>119.7569427490234</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058900206097576</v>
+        <v>-0.1058901224691788</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58900206097576</v>
+        <v>-10.58901224691788</v>
       </c>
     </row>
     <row r="99">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942916870117</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.0403930563602144</v>
+        <v>0.04039312006754003</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.03930563602144</v>
+        <v>4.039312006754003</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942916870117</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.132324990602127</v>
+        <v>-0.1323249824993521</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.2324990602127</v>
+        <v>-13.23249824993521</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982481462220356</v>
+        <v>0.004982410538207693</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.4982481462220356</v>
+        <v>0.4982410538207693</v>
       </c>
     </row>
     <row r="102">
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.6035003662109</v>
+        <v>157.603515625</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515691786884</v>
+        <v>0.1692516823827925</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92515691786884</v>
+        <v>16.92516823827926</v>
       </c>
     </row>
     <row r="104">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.6035003662109</v>
+        <v>157.603515625</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348907470703</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258307069145082</v>
+        <v>0.1258307915494528</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58307069145081</v>
+        <v>12.58307915494528</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348907470703</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.0207454681313487</v>
+        <v>-0.02074555055982463</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.07454681313487</v>
+        <v>-2.074555055982463</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125119707459349</v>
+        <v>0.07125110299903326</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125119707459349</v>
+        <v>7.125110299903326</v>
       </c>
     </row>
     <row r="107">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.0852718395616765</v>
+        <v>0.08527167560685012</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>8.527183956167651</v>
+        <v>8.527167560685012</v>
       </c>
     </row>
     <row r="108">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         <v>176.5769653320312</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258828209996035</v>
+        <v>-0.1258826889444383</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.58828209996035</v>
+        <v>-12.58826889444383</v>
       </c>
     </row>
     <row r="109">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293472316669725</v>
+        <v>-0.07293464314527709</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>-7.293472316669725</v>
+        <v>-7.293464314527709</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925888464382</v>
+        <v>-0.01569258749190239</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-1.56925888464382</v>
+        <v>-1.569258749190239</v>
       </c>
     </row>
     <row r="113">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234709050238</v>
+        <v>0.1443234582488593</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>14.43234709050238</v>
+        <v>14.43234582488593</v>
       </c>
     </row>
     <row r="114">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797470065579535</v>
+        <v>0.05797461957992356</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.797470065579535</v>
+        <v>5.797461957992356</v>
       </c>
     </row>
     <row r="115">

--- a/isolated_excel/NVIDIA Returns - Current.xlsx
+++ b/isolated_excel/NVIDIA Returns - Current.xlsx
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.68250584602356</v>
+        <v>2.682506322860718</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285933094947112</v>
+        <v>0.02285951277100851</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.285933094947112</v>
+        <v>2.285951277100851</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.68250584602356</v>
+        <v>2.682506322860718</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.496467113494873</v>
+        <v>2.496467590332031</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935259164652441</v>
+        <v>-0.06935257931854133</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-6.935259164652441</v>
+        <v>-6.935257931854133</v>
       </c>
     </row>
     <row r="4">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.496467113494873</v>
+        <v>2.496467590332031</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         <v>2.679741382598877</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341345219942963</v>
+        <v>0.07341324717236564</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7.341345219942963</v>
+        <v>7.341324717236564</v>
       </c>
     </row>
     <row r="5">
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.565840482711792</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250443741575582</v>
+        <v>-0.04250434844501383</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-4.250443741575582</v>
+        <v>-4.250434844501383</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.565840482711792</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.554834365844727</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854463634027958</v>
+        <v>0.3854463275870208</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>38.54463634027958</v>
+        <v>38.54463275870208</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.554834365844727</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.560006141662598</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.00145485704413173</v>
+        <v>0.001454588671257362</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.145485704413173</v>
+        <v>0.1454588671257362</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.560006141662598</v>
+        <v>3.56000542640686</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         <v>4.002051830291748</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699230391513</v>
+        <v>0.124170148900882</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>12.41699230391513</v>
+        <v>12.4170148900882</v>
       </c>
     </row>
     <row r="9">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.17638635635376</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.0435612864237449</v>
+        <v>0.04356152472008823</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>4.35612864237449</v>
+        <v>4.356152472008823</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.17638635635376</v>
+        <v>4.176387310028076</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406352996826172</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506388809886431</v>
+        <v>0.0550633046523048</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.506388809886431</v>
+        <v>5.50633046523048</v>
       </c>
     </row>
     <row r="11">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.406354427337646</v>
+        <v>4.406352996826172</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.097488403320312</v>
+        <v>5.097489356994629</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568493836298717</v>
+        <v>0.1568499756297945</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15.68493836298717</v>
+        <v>15.68499756297945</v>
       </c>
     </row>
     <row r="12">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.097488403320312</v>
+        <v>5.097489356994629</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.950571537017822</v>
+        <v>4.950572967529297</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882142237082763</v>
+        <v>-0.0288213234351804</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-2.882142237082763</v>
+        <v>-2.88213234351804</v>
       </c>
     </row>
     <row r="13">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.950571537017822</v>
+        <v>4.950572967529297</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772736549377441</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592220880918029</v>
+        <v>-0.03592239106832296</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-3.592220880918029</v>
+        <v>-3.592239106832296</v>
       </c>
     </row>
     <row r="14">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772736549377441</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
         <v>6.062730312347412</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840090465197</v>
+        <v>0.2702838821342943</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>27.02840090465197</v>
+        <v>27.02838821342943</v>
       </c>
     </row>
     <row r="15">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786933898926</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301664938883587</v>
+        <v>-0.04301648971692962</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.301664938883587</v>
+        <v>-4.301648971692962</v>
       </c>
     </row>
     <row r="17">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.715785980224609</v>
+        <v>5.715786933898926</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>5.550673484802246</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888710249012416</v>
+        <v>-0.02888726451950696</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.888710249012416</v>
+        <v>-2.888726451950696</v>
       </c>
     </row>
     <row r="18">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363441559658</v>
+        <v>0.1220361723436048</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.20363441559658</v>
+        <v>12.20361723436048</v>
       </c>
     </row>
     <row r="19">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.228057384490967</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.850457191467285</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062888790395171</v>
+        <v>-0.06062882062502617</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-6.062888790395171</v>
+        <v>-6.062882062502617</v>
       </c>
     </row>
     <row r="20">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.850457191467285</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047037124633789</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360045538057688</v>
+        <v>0.03360086564046827</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.360045538057688</v>
+        <v>3.360086564046827</v>
       </c>
     </row>
     <row r="21">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047037124633789</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.146914667857688</v>
+        <v>0.1469144638086999</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14.6914667857688</v>
+        <v>14.69144638086999</v>
       </c>
     </row>
     <row r="22">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.935433387756348</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835735321045</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211235080261108</v>
+        <v>0.001211372421218604</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.1211235080261108</v>
+        <v>0.1211372421218604</v>
       </c>
     </row>
     <row r="23">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.943833827972412</v>
+        <v>6.943835735321045</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>5.20948314666748</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497684599418704</v>
+        <v>-0.2497686660171804</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-24.97684599418704</v>
+        <v>-24.97686660171804</v>
       </c>
     </row>
     <row r="24">
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240500250890657</v>
+        <v>-0.2240499335565385</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-22.40500250890657</v>
+        <v>-22.40499335565385</v>
       </c>
     </row>
     <row r="25">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.042298316955566</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.30200457572937</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831368402774747</v>
+        <v>-0.183136818674309</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-18.31368402774747</v>
+        <v>-18.3136818674309</v>
       </c>
     </row>
     <row r="26">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.30200457572937</v>
+        <v>3.302005052566528</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530786514282</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677919618103357</v>
+        <v>0.07677932950184241</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7.677919618103357</v>
+        <v>7.677932950184241</v>
       </c>
     </row>
     <row r="27">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.555529832839966</v>
+        <v>3.555530786514282</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.819418430328369</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421920498347312</v>
+        <v>0.0742187827420373</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.421920498347312</v>
+        <v>7.42187827420373</v>
       </c>
     </row>
     <row r="28">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.819418430328369</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.445837020874023</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640088934931905</v>
+        <v>0.1640089139689633</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.40088934931905</v>
+        <v>16.40089139689633</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.445837020874023</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         <v>4.481489658355713</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019330738912256</v>
+        <v>0.008019438853789751</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.8019330738912256</v>
+        <v>0.8019438853789751</v>
       </c>
     </row>
     <row r="30">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.357764720916748</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480822462205</v>
+        <v>-0.2507479758447347</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-25.07480822462205</v>
+        <v>-25.07479758447347</v>
       </c>
     </row>
     <row r="31">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.357764720916748</v>
+        <v>3.357765197753906</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123878988483392</v>
+        <v>0.2123873006459764</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>21.23878988483392</v>
+        <v>21.23873006459764</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.070913314819336</v>
+        <v>4.070911884307861</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.182210922241211</v>
+        <v>4.182209014892578</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733971441168226</v>
+        <v>0.02733960688604764</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2.733971441168226</v>
+        <v>2.733960688604764</v>
       </c>
     </row>
     <row r="33">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.182210922241211</v>
+        <v>4.182209014892578</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.156324863433838</v>
+        <v>4.156327247619629</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189563197233738</v>
+        <v>-0.006188539879471766</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-0.6189563197233738</v>
+        <v>-0.6188539879471766</v>
       </c>
     </row>
     <row r="34">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.156324863433838</v>
+        <v>4.156327247619629</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.319095611572266</v>
+        <v>4.319097995758057</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916218137096039</v>
+        <v>0.03916215890643548</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.916218137096039</v>
+        <v>3.916215890643548</v>
       </c>
     </row>
     <row r="35">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.319095611572266</v>
+        <v>4.319097995758057</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.987790107727051</v>
+        <v>4.987791538238525</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548228046545519</v>
+        <v>0.1548224983867503</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>15.48228046545519</v>
+        <v>15.48224983867503</v>
       </c>
     </row>
     <row r="36">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.987790107727051</v>
+        <v>4.987791538238525</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899673370009652</v>
+        <v>0.0789967110436296</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.899673370009652</v>
+        <v>7.89967110436296</v>
       </c>
     </row>
     <row r="37">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.842668056488037</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563269372395554</v>
+        <v>0.0856324937591233</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8.563269372395554</v>
+        <v>8.56324937591233</v>
       </c>
     </row>
     <row r="38">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.842668056488037</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802430236670041</v>
+        <v>0.004802185006011594</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.4802430236670041</v>
+        <v>0.4802185006011594</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.870727062225342</v>
+        <v>5.870726108551025</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.710042953491211</v>
+        <v>6.710043907165527</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429662599486818</v>
+        <v>0.1429666080643739</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>14.29662599486818</v>
+        <v>14.29666080643739</v>
       </c>
     </row>
     <row r="40">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.710042953491211</v>
+        <v>6.710043907165527</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.54929256439209</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395654342885645</v>
+        <v>-0.02395682427677925</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-2.395654342885645</v>
+        <v>-2.395682427677925</v>
       </c>
     </row>
     <row r="41">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.549293518066406</v>
+        <v>6.54929256439209</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.261862754821777</v>
+        <v>7.261863231658936</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088009317019811</v>
+        <v>0.1088011659673027</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.88009317019811</v>
+        <v>10.88011659673027</v>
       </c>
     </row>
     <row r="42">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.261862754821777</v>
+        <v>7.261863231658936</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         <v>8.820673942565918</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146572085391054</v>
+        <v>0.2146571287808294</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>21.46572085391054</v>
+        <v>21.46571287808294</v>
       </c>
     </row>
     <row r="43">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443387985229492</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059732102863103</v>
+        <v>0.07059710479247427</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>7.059732102863103</v>
+        <v>7.059710479247427</v>
       </c>
     </row>
     <row r="44">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443387985229492</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.55399513244629</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176066277577954</v>
+        <v>0.1176070554659563</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>11.76066277577954</v>
+        <v>11.76070554659563</v>
       </c>
     </row>
     <row r="45">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.55399513244629</v>
+        <v>10.55399703979492</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.29794883728027</v>
+        <v>13.29795265197754</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599919433730087</v>
+        <v>0.2599920771093882</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25.99919433730087</v>
+        <v>25.99920771093882</v>
       </c>
     </row>
     <row r="46">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.29794883728027</v>
+        <v>13.29795265197754</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.45708179473877</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196672956150757</v>
+        <v>0.01196651098106316</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.196672956150757</v>
+        <v>1.196651098106316</v>
       </c>
     </row>
     <row r="47">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.45708179473877</v>
+        <v>13.45708274841309</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.465989112854</v>
+        <v>12.46599102020264</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364841033159564</v>
+        <v>-0.07364833424445749</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7.364841033159564</v>
+        <v>-7.364833424445749</v>
       </c>
     </row>
     <row r="48">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.465989112854</v>
+        <v>12.46599102020264</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.32877922058105</v>
+        <v>13.32878494262695</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921152424538901</v>
+        <v>0.06921181966408096</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.921152424538901</v>
+        <v>6.921181966408096</v>
       </c>
     </row>
     <row r="49">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.32877922058105</v>
+        <v>13.32878494262695</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12.98799800872803</v>
+        <v>12.98799610137939</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556732362456904</v>
+        <v>-0.02556788504837204</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>-2.556732362456904</v>
+        <v>-2.556788504837204</v>
       </c>
     </row>
     <row r="50">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>12.98799800872803</v>
+        <v>12.98799610137939</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308330535889</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998126501084554</v>
+        <v>-0.004997906952991293</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>-0.4998126501084554</v>
+        <v>-0.4997906952991293</v>
       </c>
     </row>
     <row r="51">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308330535889</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.64411067962646</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579383527242676</v>
+        <v>0.05579383115505432</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>5.579383527242676</v>
+        <v>5.579383115505432</v>
       </c>
     </row>
     <row r="52">
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.64411067962646</v>
+        <v>13.64411163330078</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636932828224614</v>
+        <v>-0.02636918664632026</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>-2.636932828224614</v>
+        <v>-2.636918664632026</v>
       </c>
     </row>
     <row r="53">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.28432464599609</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.93762302398682</v>
+        <v>14.93761825561523</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.124454830941596</v>
+        <v>0.1244542298225215</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12.4454830941596</v>
+        <v>12.44542298225215</v>
       </c>
     </row>
     <row r="54">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.93762302398682</v>
+        <v>14.93761825561523</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228103355163019</v>
+        <v>0.08228150672390133</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>8.228103355163018</v>
+        <v>8.228150672390132</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.16670608520508</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.91127586364746</v>
+        <v>19.91127395629883</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316223081379092</v>
+        <v>0.2316220448510509</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>23.16223081379092</v>
+        <v>23.16220448510509</v>
       </c>
     </row>
     <row r="56">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.91127586364746</v>
+        <v>19.91127395629883</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         <v>19.41006851196289</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.0251720359416866</v>
+        <v>-0.02517194256058053</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-2.51720359416866</v>
+        <v>-2.517194256058053</v>
       </c>
     </row>
     <row r="57">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.28683090209961</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482098009269623</v>
+        <v>0.1482101939907232</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.82098009269624</v>
+        <v>14.82101939907232</v>
       </c>
     </row>
     <row r="58">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.28683090209961</v>
+        <v>22.28683853149414</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.62515449523926</v>
+        <v>20.62515640258789</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455866714113257</v>
+        <v>-0.07455889836317886</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>-7.455866714113258</v>
+        <v>-7.455889836317886</v>
       </c>
     </row>
     <row r="59">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.62515449523926</v>
+        <v>20.62515640258789</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.45487976074219</v>
+        <v>25.45488357543945</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341667436536166</v>
+        <v>0.2341668144754319</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>23.41667436536166</v>
+        <v>23.41668144754319</v>
       </c>
     </row>
     <row r="60">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.45487976074219</v>
+        <v>25.45488357543945</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53269958496094</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537054365424</v>
+        <v>0.2780533640448715</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>27.80537054365424</v>
+        <v>27.80533640448715</v>
       </c>
     </row>
     <row r="61">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5327033996582</v>
+        <v>32.53269958496094</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         <v>29.28561210632324</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981006661035974</v>
+        <v>-0.09980996105649786</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>-9.981006661035973</v>
+        <v>-9.980996105649787</v>
       </c>
     </row>
     <row r="62">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.38161087036133</v>
+        <v>24.3816032409668</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.167454284996934</v>
+        <v>-0.1674545455137538</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>-16.7454284996934</v>
+        <v>-16.74545455137538</v>
       </c>
     </row>
     <row r="63">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.38161087036133</v>
+        <v>24.3816032409668</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124936067363305</v>
+        <v>-0.004124702671098213</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>-0.4124936067363305</v>
+        <v>-0.4124702671098213</v>
       </c>
     </row>
     <row r="64">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.17429351806641</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191569816697338</v>
+        <v>0.1191572266889214</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>11.91569816697338</v>
+        <v>11.91572266889214</v>
       </c>
     </row>
     <row r="65">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.17429351806641</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         <v>18.4710750579834</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.320273955026533</v>
+        <v>-0.3202740504457099</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-32.0273955026533</v>
+        <v>-32.02740504457099</v>
       </c>
     </row>
     <row r="66">
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.59556579589844</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739766771790112</v>
+        <v>0.006739663510413774</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.6739766771790112</v>
+        <v>0.6739663510413774</v>
       </c>
     </row>
     <row r="67">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.59556579589844</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.10013580322266</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879711556529652</v>
+        <v>-0.1879711236481391</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>-18.79711556529652</v>
+        <v>-18.79711236481391</v>
       </c>
     </row>
     <row r="68">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.10013580322266</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981661828865631</v>
+        <v>0.1981660059320538</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>19.81661828865631</v>
+        <v>19.81660059320538</v>
       </c>
     </row>
     <row r="69">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09246826171875</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.0353889465332</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689700016846472</v>
+        <v>-0.1689697210443043</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>-16.89700016846471</v>
+        <v>-16.89697210443043</v>
       </c>
     </row>
     <row r="70">
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.03538703918457</v>
+        <v>15.0353889465332</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>12.09545516967773</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341662868347</v>
+        <v>-0.195534268339187</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>-19.55341662868347</v>
+        <v>-19.5534268339187</v>
       </c>
     </row>
     <row r="71">
@@ -2863,13 +2863,13 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.44858455657959</v>
+        <v>13.44858551025391</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708943086355</v>
+        <v>0.1118709731543095</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>11.18708943086355</v>
+        <v>11.18709731543095</v>
       </c>
     </row>
     <row r="72">
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.44858455657959</v>
+        <v>13.44858551025391</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -2897,13 +2897,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.86660575866699</v>
+        <v>16.86661148071289</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541547170044127</v>
+        <v>0.2541550535446946</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>25.41547170044127</v>
+        <v>25.41550535446946</v>
       </c>
     </row>
     <row r="73">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.86660575866699</v>
+        <v>16.86661148071289</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         <v>14.56530284881592</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364413766930278</v>
+        <v>-0.1364416696577458</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>-13.64413766930278</v>
+        <v>-13.64416696577458</v>
       </c>
     </row>
     <row r="74">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.336868675327757</v>
+        <v>0.3368688062792828</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>33.6868675327757</v>
+        <v>33.68688062792828</v>
       </c>
     </row>
     <row r="75">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.13863945007324</v>
+        <v>23.13864135742188</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883094544534847</v>
+        <v>0.1883094360078374</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.83094544534847</v>
+        <v>18.83094360078374</v>
       </c>
     </row>
     <row r="76">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.13863945007324</v>
+        <v>23.13864135742188</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>27.68914031982422</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966624217283688</v>
+        <v>0.1966623230859119</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>19.66624217283688</v>
+        <v>19.66623230859119</v>
       </c>
     </row>
     <row r="77">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007984799151096</v>
+        <v>-0.001007915914793878</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>-0.1007984799151096</v>
+        <v>-0.1007915914793878</v>
       </c>
     </row>
     <row r="78">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123199462891</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3101,13 +3101,13 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365666879342</v>
+        <v>0.3634363347660106</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.34365666879342</v>
+        <v>36.34363347660106</v>
       </c>
     </row>
     <row r="79">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105733971262</v>
+        <v>0.11821058535379</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>11.82105733971262</v>
+        <v>11.821058535379</v>
       </c>
     </row>
     <row r="80">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.17256546020508</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.58601760864258</v>
+        <v>46.58601379394531</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046522093279367</v>
+        <v>0.1046522187941983</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>10.46522093279367</v>
+        <v>10.46522187941983</v>
       </c>
     </row>
     <row r="81">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.58601760864258</v>
+        <v>46.58601379394531</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619646510531018</v>
+        <v>0.05619646970695968</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>5.619646510531018</v>
+        <v>5.619646970695968</v>
       </c>
     </row>
     <row r="82">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.20398712158203</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36946487426758</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185781635581729</v>
+        <v>-0.1185781727513269</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>-11.85781635581728</v>
+        <v>-11.85781727513269</v>
       </c>
     </row>
     <row r="83">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36946487426758</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         <v>40.65856552124023</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250717958217422</v>
+        <v>-0.06250709712205382</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>-6.250717958217422</v>
+        <v>-6.250709712205382</v>
       </c>
     </row>
     <row r="84">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307373046875</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468857564818131</v>
+        <v>0.1468859441272559</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>14.68857564818131</v>
+        <v>14.68859441272559</v>
       </c>
     </row>
     <row r="85">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.63072967529297</v>
+        <v>46.6307373046875</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.37888336181641</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893439166961034</v>
+        <v>0.05893405480119052</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>5.893439166961034</v>
+        <v>5.893405480119052</v>
       </c>
     </row>
     <row r="86">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.37888336181641</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424173645114505</v>
+        <v>0.2424176337275741</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>24.24173645114504</v>
+        <v>24.24176337275741</v>
       </c>
     </row>
     <row r="87">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.34918212890625</v>
+        <v>61.34918594360352</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>78.88336181640625</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858095100706863</v>
+        <v>0.2858094301189487</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>28.58095100706863</v>
+        <v>28.58094301189487</v>
       </c>
     </row>
     <row r="88">
@@ -3475,13 +3475,13 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.15633392333984</v>
+        <v>86.15635681152344</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376038890822365</v>
+        <v>-0.04376013487480812</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-4.376038890822365</v>
+        <v>-4.376013487480812</v>
       </c>
     </row>
     <row r="90">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.15633392333984</v>
+        <v>86.15635681152344</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710911304248</v>
+        <v>0.2688708425967037</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>26.88710911304248</v>
+        <v>26.88708425967037</v>
       </c>
     </row>
     <row r="91">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.3212814331055</v>
+        <v>109.3212890625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         <v>123.1988677978516</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431366228349</v>
+        <v>0.1269430579748985</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>12.69431366228348</v>
+        <v>12.69430579748985</v>
       </c>
     </row>
     <row r="92">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277657397651536</v>
+        <v>-0.05277651204904255</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-5.277657397651536</v>
+        <v>-5.277651204904254</v>
       </c>
     </row>
     <row r="93">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         <v>119.0403747558594</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008212771048568</v>
+        <v>0.02008206101966881</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>2.008212771048568</v>
+        <v>2.008206101966881</v>
       </c>
     </row>
     <row r="94">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174281509928309</v>
+        <v>0.01742821508364489</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>1.74281509928309</v>
+        <v>1.742821508364489</v>
       </c>
     </row>
     <row r="95">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321465627039194</v>
+        <v>0.09321446141964707</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>9.321465627039194</v>
+        <v>9.321446141964707</v>
       </c>
     </row>
     <row r="96">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.4047241210938</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>137.8800506591797</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.0413529545447211</v>
+        <v>0.04135295931038252</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>4.13529545447211</v>
+        <v>4.135295931038252</v>
       </c>
     </row>
     <row r="97">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>137.8800506591797</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -3750,10 +3750,10 @@
         <v>133.9398498535156</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857701884229569</v>
+        <v>-0.02857691133769347</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2.857701884229569</v>
+        <v>-2.857691133769347</v>
       </c>
     </row>
     <row r="98">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.7569427490234</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901224691788</v>
+        <v>-0.1058901794305278</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-10.58901224691788</v>
+        <v>-10.58901794305278</v>
       </c>
     </row>
     <row r="99">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.7569427490234</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039312006754003</v>
+        <v>0.04039305893354816</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>4.039312006754003</v>
+        <v>4.039305893354816</v>
       </c>
     </row>
     <row r="100">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942840576172</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249824993521</v>
+        <v>-0.132324937470998</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>-13.23249824993521</v>
+        <v>-13.23249374709981</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         <v>108.64599609375</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982410538207693</v>
+        <v>0.004982481462220356</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.4982410538207693</v>
+        <v>0.4982481462220356</v>
       </c>
     </row>
     <row r="102">
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406354069759602</v>
+        <v>0.24063554742098</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>24.06354069759602</v>
+        <v>24.063554742098</v>
       </c>
     </row>
     <row r="103">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         <v>157.603515625</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516823827925</v>
+        <v>0.1692515500187184</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16.92516823827926</v>
+        <v>16.92515500187184</v>
       </c>
     </row>
     <row r="104">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.4348907470703</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258307915494528</v>
+        <v>0.1258305979143173</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12.58307915494528</v>
+        <v>12.58305979143173</v>
       </c>
     </row>
     <row r="105">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.4348907470703</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555055982463</v>
+        <v>-0.0207454681313487</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>-2.074555055982463</v>
+        <v>-2.07454681313487</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125110299903326</v>
+        <v>0.07125119707459349</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>7.125110299903326</v>
+        <v>7.125119707459349</v>
       </c>
     </row>
     <row r="107">
@@ -4121,13 +4121,13 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258826889444383</v>
+        <v>-0.1258827644807442</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>-12.58826889444383</v>
+        <v>-12.58827644807442</v>
       </c>
     </row>
     <row r="109">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373090631056576</v>
+        <v>0.05373099736807707</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>5.373090631056576</v>
+        <v>5.373099736807707</v>
       </c>
     </row>
     <row r="110">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293464314527709</v>
+        <v>-0.07293472316669725</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>-7.293464314527709</v>
+        <v>-7.293472316669725</v>
       </c>
     </row>
     <row r="112">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.01569258749190239</v>
+        <v>-0.0156925888464382</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-1.569258749190239</v>
+        <v>-1.56925888464382</v>
       </c>
     </row>
     <row r="113">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234582488593</v>
+        <v>0.1443234709050238</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>14.43234582488593</v>
+        <v>14.43234709050238</v>
       </c>
     </row>
     <row r="114">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>210.6584930419922</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797461957992356</v>
+        <v>0.05797470065579535</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>5.797461957992356</v>
+        <v>5.797470065579535</v>
       </c>
     </row>
     <row r="115">
